--- a/src - analytics/top_50_previsoes.xlsx
+++ b/src - analytics/top_50_previsoes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -603,17 +603,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>barrerj01</t>
+          <t>ballla01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RJ BARRETT</t>
+          <t>LAMELO BALL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -621,109 +621,109 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>CHO</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="I2" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="J2" t="n">
-        <v>1838</v>
+        <v>711</v>
       </c>
       <c r="K2" t="n">
-        <v>1170</v>
+        <v>526</v>
       </c>
       <c r="L2" t="n">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="M2" t="n">
-        <v>315</v>
+        <v>113</v>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="O2" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="Q2" t="n">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="R2" t="n">
-        <v>0.715</v>
+        <v>0.865</v>
       </c>
       <c r="S2" t="n">
-        <v>0.549</v>
+        <v>0.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0.36</v>
+        <v>0.355</v>
       </c>
       <c r="U2" t="n">
-        <v>0.495</v>
+        <v>0.433</v>
       </c>
       <c r="V2" t="n">
-        <v>707</v>
+        <v>1057</v>
       </c>
       <c r="W2" t="n">
-        <v>12.18965517241379</v>
+        <v>48.04545454545455</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3846572361262242</v>
+        <v>1.486638537271449</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.18965517241379</v>
+        <v>48.04545454545455</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03349917081260365</v>
+        <v>0.09143598615916955</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.84766050054407</v>
+        <v>53.51898734177215</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.062176165803109</v>
+        <v>2.988636363636364</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>2115</v>
+        <v>3393</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1408</v>
+        <v>-2336</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>0.7138813717783763</v>
+        <v>0.650338236848668</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brownbr01</t>
+          <t>moranja01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BRUCE BROWN</t>
+          <t>JA MORANT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PG-SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -731,109 +731,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>318</v>
+      </c>
+      <c r="K3" t="n">
+        <v>226</v>
+      </c>
+      <c r="L3" t="n">
+        <v>73</v>
+      </c>
+      <c r="M3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="n">
         <v>27</v>
       </c>
-      <c r="H3" t="n">
-        <v>67</v>
-      </c>
-      <c r="I3" t="n">
-        <v>44</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1866</v>
-      </c>
-      <c r="K3" t="n">
-        <v>726</v>
-      </c>
-      <c r="L3" t="n">
-        <v>192</v>
-      </c>
-      <c r="M3" t="n">
-        <v>284</v>
-      </c>
-      <c r="N3" t="n">
-        <v>59</v>
-      </c>
-      <c r="O3" t="n">
-        <v>17</v>
-      </c>
-      <c r="P3" t="n">
-        <v>86</v>
-      </c>
       <c r="Q3" t="n">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>0.824</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>0.538</v>
+        <v>0.555</v>
       </c>
       <c r="T3" t="n">
-        <v>0.323</v>
+        <v>0.275</v>
       </c>
       <c r="U3" t="n">
-        <v>0.478</v>
+        <v>0.471</v>
       </c>
       <c r="V3" t="n">
-        <v>707</v>
+        <v>431</v>
       </c>
       <c r="W3" t="n">
-        <v>10.55223880597015</v>
+        <v>47.88888888888889</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3788853161843516</v>
+        <v>1.355345911949686</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.06818181818182</v>
+        <v>47.88888888888889</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.03349917081260365</v>
+        <v>0.02887965692843742</v>
       </c>
       <c r="AA3" t="n">
-        <v>13.63987138263666</v>
+        <v>48.79245283018868</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.78125</v>
+        <v>3.095890410958904</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>2194</v>
+        <v>2856</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1487</v>
+        <v>-2425</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>0.7031340181997635</v>
+        <v>0.6467077820108499</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quickim01</t>
+          <t>whitmca01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IMMANUEL QUICKLEY</t>
+          <t>CAM WHITMORE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PG-SG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -841,109 +841,105 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="I4" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>1985</v>
+        <v>880</v>
       </c>
       <c r="K4" t="n">
-        <v>1156</v>
+        <v>579</v>
       </c>
       <c r="L4" t="n">
-        <v>331</v>
+        <v>33</v>
       </c>
       <c r="M4" t="n">
-        <v>259</v>
+        <v>180</v>
       </c>
       <c r="N4" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P4" t="n">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="Q4" t="n">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="R4" t="n">
-        <v>0.853</v>
+        <v>0.679</v>
       </c>
       <c r="S4" t="n">
-        <v>0.471</v>
+        <v>0.538</v>
       </c>
       <c r="T4" t="n">
-        <v>0.395</v>
+        <v>0.359</v>
       </c>
       <c r="U4" t="n">
-        <v>0.434</v>
+        <v>0.454</v>
       </c>
       <c r="V4" t="n">
-        <v>744</v>
+        <v>983</v>
       </c>
       <c r="W4" t="n">
-        <v>10.94117647058824</v>
+        <v>20.91489361702128</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3748110831234257</v>
+        <v>1.117045454545454</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.57894736842105</v>
+        <v>491.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03525230987917555</v>
+        <v>0.04889574214086749</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.49319899244333</v>
+        <v>40.21363636363636</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.492447129909365</v>
+        <v>17.54545454545455</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>2423</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-1679</v>
-      </c>
+          <t>Nivel 4: Elite</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>0.691296335846555</v>
+        <v>0.6320183705551994</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fontesi01</t>
+          <t>hendrita01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SIMONE FONTECCHIO</t>
+          <t>TAYLOR HENDRICKS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -951,109 +947,105 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J5" t="n">
+        <v>856</v>
+      </c>
+      <c r="K5" t="n">
+        <v>292</v>
+      </c>
+      <c r="L5" t="n">
+        <v>32</v>
+      </c>
+      <c r="M5" t="n">
+        <v>185</v>
+      </c>
+      <c r="N5" t="n">
         <v>28</v>
       </c>
-      <c r="H5" t="n">
-        <v>66</v>
-      </c>
-      <c r="I5" t="n">
-        <v>43</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1644</v>
-      </c>
-      <c r="K5" t="n">
-        <v>692</v>
-      </c>
-      <c r="L5" t="n">
-        <v>101</v>
-      </c>
-      <c r="M5" t="n">
-        <v>246</v>
-      </c>
-      <c r="N5" t="n">
-        <v>44</v>
-      </c>
       <c r="O5" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="P5" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="Q5" t="n">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.793</v>
       </c>
       <c r="S5" t="n">
-        <v>0.551</v>
+        <v>0.55</v>
       </c>
       <c r="T5" t="n">
-        <v>0.401</v>
+        <v>0.379</v>
       </c>
       <c r="U5" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="V5" t="n">
-        <v>461</v>
+        <v>776</v>
       </c>
       <c r="W5" t="n">
-        <v>6.984848484848484</v>
+        <v>19.4</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2804136253041363</v>
+        <v>0.9065420560747663</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.72093023255814</v>
+        <v>33.73913043478261</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02184316512674721</v>
+        <v>0.0453774633062394</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.09489051094891</v>
+        <v>32.63551401869159</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.851485148514851</v>
+        <v>9.125</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>549</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-88</v>
-      </c>
+          <t>Nivel 3: Above Average</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>0.6883048242191933</v>
+        <v>0.631316291579607</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>anunoog01</t>
+          <t>jacksgg01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OG ANUNOBY</t>
+          <t>GG JACKSON II</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1061,109 +1053,105 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>1702</v>
+        <v>1233</v>
       </c>
       <c r="K6" t="n">
-        <v>733</v>
+        <v>699</v>
       </c>
       <c r="L6" t="n">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="N6" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="O6" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P6" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="Q6" t="n">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="R6" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="S6" t="n">
-        <v>0.581</v>
+        <v>0.502</v>
       </c>
       <c r="T6" t="n">
-        <v>0.382</v>
+        <v>0.357</v>
       </c>
       <c r="U6" t="n">
-        <v>0.489</v>
+        <v>0.428</v>
       </c>
       <c r="V6" t="n">
-        <v>721</v>
+        <v>1156</v>
       </c>
       <c r="W6" t="n">
-        <v>14.42</v>
+        <v>24.08333333333333</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4236192714453584</v>
+        <v>0.9375506893755069</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.42</v>
+        <v>64.22222222222223</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03416252072968491</v>
+        <v>0.07745912623961404</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.2502937720329</v>
+        <v>33.75182481751825</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.850467289719626</v>
+        <v>11.84745762711864</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>2321</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-1600</v>
-      </c>
+          <t>Nivel 3: Above Average</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>0.687284928447104</v>
+        <v>0.6305571728262869</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>washipj01</t>
+          <t>herroty01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P.J. WASHINGTON</t>
+          <t>TYLER HERRO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1171,109 +1159,109 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="I7" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J7" t="n">
-        <v>2221</v>
+        <v>1407</v>
       </c>
       <c r="K7" t="n">
-        <v>939</v>
+        <v>875</v>
       </c>
       <c r="L7" t="n">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="M7" t="n">
-        <v>411</v>
+        <v>222</v>
       </c>
       <c r="N7" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="O7" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q7" t="n">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.856</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.478</v>
       </c>
       <c r="T7" t="n">
-        <v>0.32</v>
+        <v>0.396</v>
       </c>
       <c r="U7" t="n">
-        <v>0.436</v>
+        <v>0.441</v>
       </c>
       <c r="V7" t="n">
-        <v>839</v>
+        <v>1517</v>
       </c>
       <c r="W7" t="n">
-        <v>11.49315068493151</v>
+        <v>36.11904761904762</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3777577667717245</v>
+        <v>1.07818052594172</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.64444444444445</v>
+        <v>37.925</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03975361288794125</v>
+        <v>0.08956721969652241</v>
       </c>
       <c r="AA7" t="n">
-        <v>13.59927960378208</v>
+        <v>38.81449893390192</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.659574468085107</v>
+        <v>4.654255319148936</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>2334</v>
+        <v>2406</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1495</v>
+        <v>-889</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>0.6866771130188583</v>
+        <v>0.6277049815372435</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>achiupr01</t>
+          <t>pippesc02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PRECIOUS ACHIUWA</t>
+          <t>SCOTTY PIPPEN JR.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PF-C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1281,109 +1269,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
+        <v>23</v>
+      </c>
+      <c r="H8" t="n">
+        <v>21</v>
+      </c>
+      <c r="I8" t="n">
+        <v>16</v>
+      </c>
+      <c r="J8" t="n">
+        <v>527</v>
+      </c>
+      <c r="K8" t="n">
+        <v>271</v>
+      </c>
+      <c r="L8" t="n">
+        <v>98</v>
+      </c>
+      <c r="M8" t="n">
+        <v>67</v>
+      </c>
+      <c r="N8" t="n">
+        <v>36</v>
+      </c>
+      <c r="O8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>60</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="V8" t="n">
+        <v>631</v>
+      </c>
+      <c r="W8" t="n">
+        <v>30.04761904761905</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.197343453510436</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>39.4375</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.04228088984186545</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>43.10436432637571</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.76530612244898</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Nivel 4: Elite</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
         <v>24</v>
       </c>
-      <c r="H8" t="n">
-        <v>74</v>
-      </c>
-      <c r="I8" t="n">
-        <v>18</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1624</v>
-      </c>
-      <c r="K8" t="n">
-        <v>565</v>
-      </c>
-      <c r="L8" t="n">
-        <v>97</v>
-      </c>
-      <c r="M8" t="n">
-        <v>487</v>
-      </c>
-      <c r="N8" t="n">
-        <v>46</v>
-      </c>
-      <c r="O8" t="n">
-        <v>68</v>
-      </c>
-      <c r="P8" t="n">
-        <v>83</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>143</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.616</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.268</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="V8" t="n">
-        <v>473</v>
-      </c>
-      <c r="W8" t="n">
-        <v>6.391891891891892</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.291256157635468</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>26.27777777777778</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.02241175076995973</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10.48522167487685</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>5.824742268041237</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>1419</v>
-      </c>
       <c r="AE8" t="n">
-        <v>-946</v>
+        <v>607</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>0.6829947715355261</v>
+        <v>0.6171617140402206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dinwisp01</t>
+          <t>clownno01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SPENCER DINWIDDIE</t>
+          <t>NOAH CLOWNEY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1391,109 +1379,105 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>BRK</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="I9" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>2152</v>
+        <v>370</v>
       </c>
       <c r="K9" t="n">
-        <v>795</v>
+        <v>133</v>
       </c>
       <c r="L9" t="n">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="M9" t="n">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="N9" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P9" t="n">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>0.805</v>
+        <v>0.7</v>
       </c>
       <c r="S9" t="n">
-        <v>0.467</v>
+        <v>0.633</v>
       </c>
       <c r="T9" t="n">
-        <v>0.337</v>
+        <v>0.364</v>
       </c>
       <c r="U9" t="n">
-        <v>0.392</v>
+        <v>0.538</v>
       </c>
       <c r="V9" t="n">
-        <v>440</v>
+        <v>335</v>
       </c>
       <c r="W9" t="n">
-        <v>5.789473684210527</v>
+        <v>14.56521739130435</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2044609665427509</v>
+        <v>0.9054054054054054</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.461538461538462</v>
+        <v>83.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02084814025112533</v>
+        <v>0.02088268295723725</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.360594795539033</v>
+        <v>32.5945945945946</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.23314606741573</v>
+        <v>7.388888888888889</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD9" t="n">
-        <v>2474</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-2034</v>
-      </c>
+          <t>Nivel 3: Above Average</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>0.6717134044032168</v>
+        <v>0.6142060419111436</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bogdabo02</t>
+          <t>easonta01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BOJAN BOGDANOVIC</t>
+          <t>TARI EASON</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SF-PF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1501,109 +1485,109 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H10" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>480</v>
+      </c>
+      <c r="K10" t="n">
+        <v>215</v>
+      </c>
+      <c r="L10" t="n">
         <v>27</v>
       </c>
-      <c r="J10" t="n">
-        <v>1478</v>
-      </c>
-      <c r="K10" t="n">
-        <v>868</v>
-      </c>
-      <c r="L10" t="n">
-        <v>97</v>
-      </c>
       <c r="M10" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="P10" t="n">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="Q10" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="R10" t="n">
-        <v>0.785</v>
+        <v>0.636</v>
       </c>
       <c r="S10" t="n">
-        <v>0.507</v>
+        <v>0.504</v>
       </c>
       <c r="T10" t="n">
-        <v>0.398</v>
+        <v>0.36</v>
       </c>
       <c r="U10" t="n">
-        <v>0.454</v>
+        <v>0.466</v>
       </c>
       <c r="V10" t="n">
-        <v>404</v>
+        <v>589</v>
       </c>
       <c r="W10" t="n">
-        <v>7.087719298245614</v>
+        <v>26.77272727272727</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2733423545331529</v>
+        <v>1.227083333333333</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.96296296296296</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0191423833214878</v>
+        <v>0.02929765220851572</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.840324763193506</v>
+        <v>44.175</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.948453608247423</v>
+        <v>7.962962962962963</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2277</v>
+        <v>1811</v>
       </c>
       <c r="AE10" t="n">
-        <v>-1873</v>
+        <v>-1222</v>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>0.6593897476979259</v>
+        <v>0.6094643480276508</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hieldbu01</t>
+          <t>banede01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BUDDY HIELD</t>
+          <t>DESMOND BANE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SF-SG</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1611,109 +1595,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="I11" t="n">
         <v>42</v>
       </c>
       <c r="J11" t="n">
-        <v>2160</v>
+        <v>1443</v>
       </c>
       <c r="K11" t="n">
-        <v>1013</v>
+        <v>997</v>
       </c>
       <c r="L11" t="n">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="M11" t="n">
-        <v>269</v>
+        <v>185</v>
       </c>
       <c r="N11" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="O11" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="P11" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="Q11" t="n">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="R11" t="n">
-        <v>0.881</v>
+        <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>0.539</v>
+        <v>0.536</v>
       </c>
       <c r="T11" t="n">
-        <v>0.386</v>
+        <v>0.381</v>
       </c>
       <c r="U11" t="n">
-        <v>0.436</v>
+        <v>0.464</v>
       </c>
       <c r="V11" t="n">
-        <v>834</v>
+        <v>1824</v>
       </c>
       <c r="W11" t="n">
-        <v>9.928571428571429</v>
+        <v>43.42857142857143</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3861111111111111</v>
+        <v>1.264033264033264</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.85714285714286</v>
+        <v>43.42857142857143</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.03951670220326937</v>
+        <v>0.1222192441704637</v>
       </c>
       <c r="AA11" t="n">
-        <v>13.9</v>
+        <v>45.50519750519751</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.292372881355933</v>
+        <v>4.334782608695652</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>2826</v>
+        <v>2591</v>
       </c>
       <c r="AE11" t="n">
-        <v>-1992</v>
+        <v>-767</v>
       </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>0.6490254260446224</v>
+        <v>0.6038305573573519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>willigr01</t>
+          <t>simonan01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRANT WILLIAMS</t>
+          <t>ANFERNEE SIMONS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1721,109 +1705,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="I12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J12" t="n">
-        <v>2130</v>
+        <v>1582</v>
       </c>
       <c r="K12" t="n">
-        <v>784</v>
+        <v>1039</v>
       </c>
       <c r="L12" t="n">
-        <v>174</v>
+        <v>255</v>
       </c>
       <c r="M12" t="n">
-        <v>318</v>
+        <v>167</v>
       </c>
       <c r="N12" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="O12" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="Q12" t="n">
-        <v>226</v>
+        <v>98</v>
       </c>
       <c r="R12" t="n">
-        <v>0.757</v>
+        <v>0.916</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.472</v>
       </c>
       <c r="T12" t="n">
-        <v>0.375</v>
+        <v>0.385</v>
       </c>
       <c r="U12" t="n">
-        <v>0.456</v>
+        <v>0.43</v>
       </c>
       <c r="V12" t="n">
-        <v>814</v>
+        <v>1693</v>
       </c>
       <c r="W12" t="n">
-        <v>10.71052631578947</v>
+        <v>36.80434782608695</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3821596244131455</v>
+        <v>1.070164348925411</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.93023255813954</v>
+        <v>36.80434782608695</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.03856905946458185</v>
+        <v>0.1009661259541985</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.75774647887324</v>
+        <v>38.52591656131479</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.505747126436781</v>
+        <v>4.074509803921568</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1494</v>
+        <v>2161</v>
       </c>
       <c r="AE12" t="n">
-        <v>-680</v>
+        <v>-468</v>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>0.644935797721824</v>
+        <v>0.5935210119967944</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>agbajoc01</t>
+          <t>livelde01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OCHAI AGBAJI</t>
+          <t>DERECK LIVELY II</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1831,104 +1815,100 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="I13" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="J13" t="n">
-        <v>1641</v>
+        <v>1294</v>
       </c>
       <c r="K13" t="n">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="L13" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="M13" t="n">
-        <v>216</v>
+        <v>378</v>
       </c>
       <c r="N13" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="O13" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="P13" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="R13" t="n">
-        <v>0.661</v>
+        <v>0.506</v>
       </c>
       <c r="S13" t="n">
-        <v>0.523</v>
+        <v>0.752</v>
       </c>
       <c r="T13" t="n">
-        <v>0.294</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.411</v>
+        <v>0.747</v>
       </c>
       <c r="V13" t="n">
-        <v>423</v>
+        <v>1441</v>
       </c>
       <c r="W13" t="n">
-        <v>5.423076923076923</v>
+        <v>26.2</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2577696526508227</v>
+        <v>1.113601236476043</v>
       </c>
       <c r="Y13" t="n">
-        <v>15.10714285714286</v>
+        <v>34.30952380952381</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.02004264392324094</v>
+        <v>0.08288754673569169</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.279707495429617</v>
+        <v>40.08964451313756</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.481927710843373</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD13" t="n">
-        <v>842</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>-419</v>
-      </c>
+          <t>Nivel 4: Elite</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>0.6446645634394659</v>
+        <v>0.5869397280156621</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>schrode01</t>
+          <t>portecr01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DENNIS SCHRODER</t>
+          <t>CRAIG PORTER JR.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1941,109 +1921,105 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="I14" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>2486</v>
+        <v>649</v>
       </c>
       <c r="K14" t="n">
-        <v>1122</v>
+        <v>285</v>
       </c>
       <c r="L14" t="n">
-        <v>488</v>
+        <v>118</v>
       </c>
       <c r="M14" t="n">
-        <v>242</v>
+        <v>109</v>
       </c>
       <c r="N14" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="O14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P14" t="n">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="Q14" t="n">
-        <v>164</v>
+        <v>40</v>
       </c>
       <c r="R14" t="n">
-        <v>0.836</v>
+        <v>0.732</v>
       </c>
       <c r="S14" t="n">
-        <v>0.474</v>
+        <v>0.536</v>
       </c>
       <c r="T14" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="U14" t="n">
-        <v>0.435</v>
+        <v>0.509</v>
       </c>
       <c r="V14" t="n">
-        <v>858</v>
+        <v>695</v>
       </c>
       <c r="W14" t="n">
-        <v>10.725</v>
+        <v>13.62745098039216</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3451327433628318</v>
+        <v>1.070878274268105</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.79310344827586</v>
+        <v>115.8333333333333</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.04065387348969438</v>
+        <v>0.03417752643225965</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.42477876106195</v>
+        <v>38.55161787365176</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.299180327868852</v>
+        <v>2.415254237288135</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD14" t="n">
-        <v>2543</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-1685</v>
-      </c>
+          <t>Nivel 4: Elite</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="n">
-        <v>0.6425035953233252</v>
+        <v>0.5856165942406759</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lowryky01</t>
+          <t>lavinza01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KYLE LOWRY</t>
+          <t>ZACH LAVINE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2051,109 +2027,109 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I15" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>1690</v>
+        <v>872</v>
       </c>
       <c r="K15" t="n">
         <v>487</v>
       </c>
       <c r="L15" t="n">
-        <v>253</v>
+        <v>98</v>
       </c>
       <c r="M15" t="n">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="N15" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="O15" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="Q15" t="n">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="R15" t="n">
-        <v>0.84</v>
+        <v>0.854</v>
       </c>
       <c r="S15" t="n">
-        <v>0.512</v>
+        <v>0.536</v>
       </c>
       <c r="T15" t="n">
-        <v>0.392</v>
+        <v>0.349</v>
       </c>
       <c r="U15" t="n">
-        <v>0.432</v>
+        <v>0.452</v>
       </c>
       <c r="V15" t="n">
-        <v>534</v>
+        <v>883</v>
       </c>
       <c r="W15" t="n">
-        <v>8.9</v>
+        <v>35.32</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3159763313609468</v>
+        <v>1.012614678899083</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.709090909090909</v>
+        <v>38.39130434782609</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.02530206112295665</v>
+        <v>0.04416545791026859</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.37514792899408</v>
+        <v>36.45412844036697</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.924901185770751</v>
+        <v>4.969387755102041</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>3373</v>
+        <v>3105</v>
       </c>
       <c r="AE15" t="n">
-        <v>-2839</v>
+        <v>-2222</v>
       </c>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="n">
-        <v>0.6414912773036293</v>
+        <v>0.5850650024355742</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>manntr01</t>
+          <t>meltode01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRE MANN</t>
+          <t>DE'ANTHONY MELTON</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2161,109 +2137,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H16" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J16" t="n">
-        <v>987</v>
+        <v>1023</v>
       </c>
       <c r="K16" t="n">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="L16" t="n">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="M16" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="N16" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="P16" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="Q16" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="R16" t="n">
-        <v>0.763</v>
+        <v>0.835</v>
       </c>
       <c r="S16" t="n">
-        <v>0.516</v>
+        <v>0.425</v>
       </c>
       <c r="T16" t="n">
-        <v>0.373</v>
+        <v>0.36</v>
       </c>
       <c r="U16" t="n">
-        <v>0.459</v>
+        <v>0.386</v>
       </c>
       <c r="V16" t="n">
-        <v>118</v>
+        <v>1058</v>
       </c>
       <c r="W16" t="n">
-        <v>2.878048780487805</v>
+        <v>27.84210526315789</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1195542046605876</v>
+        <v>1.034213098729228</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.214285714285714</v>
+        <v>32.06060606060606</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.005591092158256337</v>
+        <v>0.07040660145072203</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.303951367781155</v>
+        <v>37.2316715542522</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.315151515151515</v>
+        <v>3.692982456140351</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1103</v>
+        <v>2081</v>
       </c>
       <c r="AE16" t="n">
-        <v>-985</v>
+        <v>-1023</v>
       </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>0.6382897823304464</v>
+        <v>0.5843281535153161</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>haywago01</t>
+          <t>vukcetr01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GORDON HAYWARD</t>
+          <t>TRISTAN VUKCEVIC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2271,109 +2247,105 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>153</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85</v>
+      </c>
+      <c r="L17" t="n">
+        <v>13</v>
+      </c>
+      <c r="M17" t="n">
+        <v>36</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="n">
         <v>28</v>
       </c>
-      <c r="J17" t="n">
-        <v>1245</v>
-      </c>
-      <c r="K17" t="n">
-        <v>500</v>
-      </c>
-      <c r="L17" t="n">
-        <v>158</v>
-      </c>
-      <c r="M17" t="n">
-        <v>181</v>
-      </c>
-      <c r="N17" t="n">
-        <v>40</v>
-      </c>
-      <c r="O17" t="n">
-        <v>13</v>
-      </c>
-      <c r="P17" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>67</v>
-      </c>
       <c r="R17" t="n">
-        <v>0.742</v>
+        <v>0.773</v>
       </c>
       <c r="S17" t="n">
-        <v>0.479</v>
+        <v>0.613</v>
       </c>
       <c r="T17" t="n">
-        <v>0.411</v>
+        <v>0.278</v>
       </c>
       <c r="U17" t="n">
-        <v>0.464</v>
+        <v>0.433</v>
       </c>
       <c r="V17" t="n">
-        <v>300</v>
+        <v>187</v>
       </c>
       <c r="W17" t="n">
-        <v>5.882352941176471</v>
+        <v>18.7</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2409638554216867</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="Y17" t="n">
-        <v>10.71428571428571</v>
+        <v>46.75</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.01421464108031272</v>
+        <v>0.0112888620585572</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.674698795180722</v>
+        <v>44</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.164556962025316</v>
+        <v>6.538461538461538</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD17" t="n">
-        <v>2683</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-2383</v>
-      </c>
+          <t>Nivel 4: Elite</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="n">
-        <v>0.6315889890929227</v>
+        <v>0.580712699034567</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>batumni01</t>
+          <t>hortota01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NICOLAS BATUM</t>
+          <t>TALEN HORTON-TUCKER</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2381,104 +2353,104 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I18" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>1529</v>
+        <v>1009</v>
       </c>
       <c r="K18" t="n">
-        <v>320</v>
+        <v>516</v>
       </c>
       <c r="L18" t="n">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="M18" t="n">
-        <v>248</v>
+        <v>121</v>
       </c>
       <c r="N18" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O18" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="P18" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Q18" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="R18" t="n">
-        <v>0.714</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>0.606</v>
+        <v>0.438</v>
       </c>
       <c r="T18" t="n">
-        <v>0.395</v>
+        <v>0.33</v>
       </c>
       <c r="U18" t="n">
-        <v>0.453</v>
+        <v>0.396</v>
       </c>
       <c r="V18" t="n">
-        <v>54</v>
+        <v>1121</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9</v>
+        <v>21.98039215686275</v>
       </c>
       <c r="X18" t="n">
-        <v>0.03531720078482668</v>
+        <v>1.111000991080278</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.421052631578947</v>
+        <v>101.9090909090909</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.00255863539445629</v>
+        <v>0.06555172212151336</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.271419228253761</v>
+        <v>39.99603567889</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>2.915254237288135</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2669</v>
+        <v>1432</v>
       </c>
       <c r="AE18" t="n">
-        <v>-2615</v>
+        <v>-311</v>
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>0.6314277187548235</v>
+        <v>0.5767584356561199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>baglema01</t>
+          <t>okongon01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MARVIN BAGLEY III</t>
+          <t>ONYEKA OKONGWU</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2491,104 +2463,104 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>1053</v>
+        <v>1405</v>
       </c>
       <c r="K19" t="n">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="L19" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="M19" t="n">
-        <v>312</v>
+        <v>376</v>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O19" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="Q19" t="n">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="R19" t="n">
-        <v>0.762</v>
+        <v>0.793</v>
       </c>
       <c r="S19" t="n">
-        <v>0.597</v>
+        <v>0.676</v>
       </c>
       <c r="T19" t="n">
-        <v>0.391</v>
+        <v>0.333</v>
       </c>
       <c r="U19" t="n">
-        <v>0.586</v>
+        <v>0.611</v>
       </c>
       <c r="V19" t="n">
-        <v>482</v>
+        <v>1442</v>
       </c>
       <c r="W19" t="n">
-        <v>9.640000000000001</v>
+        <v>26.21818181818182</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4577397910731244</v>
+        <v>1.026334519572954</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.28</v>
+        <v>180.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.02283819000236911</v>
+        <v>0.07056866007634335</v>
       </c>
       <c r="AA19" t="n">
-        <v>16.47863247863248</v>
+        <v>36.94804270462633</v>
       </c>
       <c r="AB19" t="n">
-        <v>10.6</v>
+        <v>7.581081081081081</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1681</v>
+        <v>2122</v>
       </c>
       <c r="AE19" t="n">
-        <v>-1199</v>
+        <v>-680</v>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="n">
-        <v>0.6221788335377743</v>
+        <v>0.5764877474787679</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>onealro01</t>
+          <t>murphtr02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ROYCE O'NEALE</t>
+          <t>TREY MURPHY III</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2601,109 +2573,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H20" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>1954</v>
+        <v>1690</v>
       </c>
       <c r="K20" t="n">
-        <v>608</v>
+        <v>842</v>
       </c>
       <c r="L20" t="n">
-        <v>219</v>
+        <v>124</v>
       </c>
       <c r="M20" t="n">
-        <v>377</v>
+        <v>280</v>
       </c>
       <c r="N20" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="O20" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="P20" t="n">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="Q20" t="n">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>0.496</v>
+        <v>0.602</v>
       </c>
       <c r="T20" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="U20" t="n">
-        <v>0.397</v>
+        <v>0.443</v>
       </c>
       <c r="V20" t="n">
-        <v>744</v>
+        <v>1795</v>
       </c>
       <c r="W20" t="n">
-        <v>9.417721518987342</v>
+        <v>31.49122807017544</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3807574206755374</v>
+        <v>1.062130177514793</v>
       </c>
       <c r="Y20" t="n">
-        <v>53.14285714285715</v>
+        <v>78.04347826086956</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.03525230987917555</v>
+        <v>0.0871401524345842</v>
       </c>
       <c r="AA20" t="n">
-        <v>13.70726714431935</v>
+        <v>38.23668639053254</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.776255707762557</v>
+        <v>6.790322580645161</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1951</v>
+        <v>2310</v>
       </c>
       <c r="AE20" t="n">
-        <v>-1207</v>
+        <v>-515</v>
       </c>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="n">
-        <v>0.6143626056299974</v>
+        <v>0.5740312665957932</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bantoda01</t>
+          <t>mobleev01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DALANO BANTON</t>
+          <t>EVAN MOBLEY</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2711,109 +2683,109 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H21" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I21" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="J21" t="n">
-        <v>1047</v>
+        <v>1532</v>
       </c>
       <c r="K21" t="n">
-        <v>557</v>
+        <v>785</v>
       </c>
       <c r="L21" t="n">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="M21" t="n">
-        <v>178</v>
+        <v>468</v>
       </c>
       <c r="N21" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="P21" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="Q21" t="n">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="R21" t="n">
-        <v>0.783</v>
+        <v>0.719</v>
       </c>
       <c r="S21" t="n">
-        <v>0.475</v>
+        <v>0.604</v>
       </c>
       <c r="T21" t="n">
-        <v>0.296</v>
+        <v>0.373</v>
       </c>
       <c r="U21" t="n">
-        <v>0.404</v>
+        <v>0.58</v>
       </c>
       <c r="V21" t="n">
-        <v>138</v>
+        <v>1938</v>
       </c>
       <c r="W21" t="n">
-        <v>2.555555555555555</v>
+        <v>38.76</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1318051575931232</v>
+        <v>1.265013054830287</v>
       </c>
       <c r="Y21" t="n">
-        <v>15.33333333333333</v>
+        <v>38.76</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.006538734896943853</v>
+        <v>0.09530366363412834</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.744985673352435</v>
+        <v>45.54046997389034</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.385826771653544</v>
+        <v>4.90625</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>557</v>
+        <v>2944</v>
       </c>
       <c r="AE21" t="n">
-        <v>-419</v>
+        <v>-1006</v>
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="n">
-        <v>0.6113907863449268</v>
+        <v>0.5730532806671426</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tillmxa01</t>
+          <t>prospol01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XAVIER TILLMAN SR.</t>
+          <t>OLIVIER-MAXENCE PROSPER</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C-PF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2821,109 +2793,105 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="I22" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>974</v>
+        <v>336</v>
       </c>
       <c r="K22" t="n">
-        <v>284</v>
+        <v>121</v>
       </c>
       <c r="L22" t="n">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="M22" t="n">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="N22" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="O22" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="Q22" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>0.44</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>0.51</v>
+        <v>0.458</v>
       </c>
       <c r="T22" t="n">
-        <v>0.247</v>
+        <v>0.289</v>
       </c>
       <c r="U22" t="n">
-        <v>0.434</v>
+        <v>0.385</v>
       </c>
       <c r="V22" t="n">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="W22" t="n">
-        <v>4.722222222222222</v>
+        <v>6.675</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2618069815195072</v>
+        <v>0.7946428571428571</v>
       </c>
       <c r="Y22" t="n">
-        <v>17</v>
+        <v>267</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.01208244491826581</v>
+        <v>0.01535806729939603</v>
       </c>
       <c r="AA22" t="n">
-        <v>9.42505133470226</v>
+        <v>28.60714285714285</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.688311688311688</v>
+        <v>5.5</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD22" t="n">
-        <v>1229</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>-974</v>
-      </c>
+          <t>Nivel 2: Average</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="n">
-        <v>0.6105287313496028</v>
+        <v>0.5721092020284226</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>martike04</t>
+          <t>willima07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KJ MARTIN</t>
+          <t>MARK WILLIAMS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2931,109 +2899,107 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>CHO</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>746</v>
+        <v>508</v>
       </c>
       <c r="K23" t="n">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="L23" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="M23" t="n">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="N23" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O23" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P23" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="Q23" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R23" t="n">
-        <v>0.537</v>
+        <v>0.719</v>
       </c>
       <c r="S23" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.286</v>
-      </c>
+        <v>0.649</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
-        <v>0.536</v>
+        <v>0.649</v>
       </c>
       <c r="V23" t="n">
-        <v>24</v>
+        <v>607</v>
       </c>
       <c r="W23" t="n">
-        <v>0.4</v>
+        <v>31.94736842105263</v>
       </c>
       <c r="X23" t="n">
-        <v>0.032171581769437</v>
+        <v>1.19488188976378</v>
       </c>
       <c r="Y23" t="n">
-        <v>12</v>
+        <v>31.94736842105263</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.001137171286425018</v>
+        <v>0.05250865051903114</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.158176943699732</v>
+        <v>43.01574803149607</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.392156862745098</v>
+        <v>11</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2016</v>
+        <v>978</v>
       </c>
       <c r="AE23" t="n">
-        <v>-1992</v>
+        <v>-371</v>
       </c>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="n">
-        <v>0.6089510442324656</v>
+        <v>0.5717725538363014</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>roddyda01</t>
+          <t>robinmi01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAVID RODDY</t>
+          <t>MITCHELL ROBINSON</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -3041,109 +3007,107 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H24" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="I24" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>1177</v>
+        <v>768</v>
       </c>
       <c r="K24" t="n">
-        <v>425</v>
+        <v>173</v>
       </c>
       <c r="L24" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="M24" t="n">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="N24" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="O24" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="P24" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="Q24" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.409</v>
       </c>
       <c r="S24" t="n">
-        <v>0.478</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.293</v>
-      </c>
+        <v>0.575</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
-        <v>0.403</v>
+        <v>0.575</v>
       </c>
       <c r="V24" t="n">
-        <v>47</v>
+        <v>690</v>
       </c>
       <c r="W24" t="n">
-        <v>0.7230769230769231</v>
+        <v>22.25806451612903</v>
       </c>
       <c r="X24" t="n">
-        <v>0.03993203058623619</v>
+        <v>0.8984375</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.615384615384615</v>
+        <v>32.85714285714285</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.00222696043591566</v>
+        <v>0.0459662913863167</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.437553101104503</v>
+        <v>32.34375</v>
       </c>
       <c r="AB24" t="n">
-        <v>5.3125</v>
+        <v>9.611111111111111</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 3: Above Average</t>
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>918</v>
+        <v>2033</v>
       </c>
       <c r="AE24" t="n">
-        <v>-871</v>
+        <v>-1343</v>
       </c>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="n">
-        <v>0.6012051070989139</v>
+        <v>0.5695564455146348</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>jacksgg01</t>
+          <t>thompam01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GG JACKSON II</t>
+          <t>AMEN THOMPSON</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3151,81 +3115,81 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H25" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>1233</v>
+        <v>1388</v>
       </c>
       <c r="K25" t="n">
-        <v>699</v>
+        <v>592</v>
       </c>
       <c r="L25" t="n">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="M25" t="n">
-        <v>196</v>
+        <v>409</v>
       </c>
       <c r="N25" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="O25" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="P25" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="Q25" t="n">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="R25" t="n">
-        <v>0.752</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>0.502</v>
+        <v>0.595</v>
       </c>
       <c r="T25" t="n">
-        <v>0.357</v>
+        <v>0.138</v>
       </c>
       <c r="U25" t="n">
-        <v>0.428</v>
+        <v>0.536</v>
       </c>
       <c r="V25" t="n">
-        <v>1156</v>
+        <v>1644</v>
       </c>
       <c r="W25" t="n">
-        <v>24.08333333333333</v>
+        <v>26.51612903225806</v>
       </c>
       <c r="X25" t="n">
-        <v>0.9375506893755069</v>
+        <v>1.184438040345821</v>
       </c>
       <c r="Y25" t="n">
-        <v>64.22222222222223</v>
+        <v>71.47826086956522</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.07745912623961404</v>
+        <v>0.08177477118981297</v>
       </c>
       <c r="AA25" t="n">
-        <v>33.75182481751825</v>
+        <v>42.63976945244956</v>
       </c>
       <c r="AB25" t="n">
-        <v>11.84745762711864</v>
+        <v>3.631901840490797</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Nivel 3: Above Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -3233,18 +3197,18 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="n">
-        <v>0.597025634643053</v>
+        <v>0.5683309777078436</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>micicva01</t>
+          <t>youngtr01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VASILIJE MICIC</t>
+          <t>TRAE YOUNG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3257,105 +3221,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="J26" t="n">
-        <v>1176</v>
+        <v>1942</v>
       </c>
       <c r="K26" t="n">
-        <v>422</v>
+        <v>1389</v>
       </c>
       <c r="L26" t="n">
-        <v>262</v>
+        <v>583</v>
       </c>
       <c r="M26" t="n">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="N26" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="O26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P26" t="n">
-        <v>99</v>
+        <v>235</v>
       </c>
       <c r="Q26" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.855</v>
       </c>
       <c r="S26" t="n">
-        <v>0.537</v>
+        <v>0.479</v>
       </c>
       <c r="T26" t="n">
-        <v>0.279</v>
+        <v>0.373</v>
       </c>
       <c r="U26" t="n">
         <v>0.43</v>
       </c>
       <c r="V26" t="n">
-        <v>277</v>
+        <v>2659</v>
       </c>
       <c r="W26" t="n">
-        <v>4.616666666666666</v>
+        <v>49.24074074074074</v>
       </c>
       <c r="X26" t="n">
-        <v>0.2355442176870748</v>
+        <v>1.369207003089598</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.19047619047619</v>
+        <v>49.24074074074074</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.01312485193082208</v>
+        <v>0.1301262601546442</v>
       </c>
       <c r="AA26" t="n">
-        <v>8.479591836734695</v>
+        <v>49.29145211122555</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.610687022900763</v>
+        <v>2.382504288164665</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
+          <t>Nivel 4: Elite</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>3825</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>-1166</v>
+      </c>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="n">
-        <v>0.5953764178503536</v>
+        <v>0.5665517955243703</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>beverpa01</t>
+          <t>bolbo01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PATRICK BEVERLEY</t>
+          <t>BOL BOL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3363,109 +3331,109 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H27" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="I27" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1462</v>
+        <v>469</v>
       </c>
       <c r="K27" t="n">
-        <v>451</v>
+        <v>223</v>
       </c>
       <c r="L27" t="n">
-        <v>212</v>
+        <v>17</v>
       </c>
       <c r="M27" t="n">
-        <v>239</v>
+        <v>137</v>
       </c>
       <c r="N27" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="O27" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="P27" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="Q27" t="n">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="R27" t="n">
-        <v>0.822</v>
+        <v>0.789</v>
       </c>
       <c r="S27" t="n">
-        <v>0.49</v>
+        <v>0.717</v>
       </c>
       <c r="T27" t="n">
-        <v>0.337</v>
+        <v>0.423</v>
       </c>
       <c r="U27" t="n">
-        <v>0.417</v>
+        <v>0.616</v>
       </c>
       <c r="V27" t="n">
-        <v>495</v>
+        <v>557</v>
       </c>
       <c r="W27" t="n">
-        <v>6.780821917808219</v>
+        <v>12.95348837209302</v>
       </c>
       <c r="X27" t="n">
-        <v>0.3385772913816689</v>
+        <v>1.187633262260128</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.07692307692308</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.02345415778251599</v>
+        <v>0.03046712613499617</v>
       </c>
       <c r="AA27" t="n">
-        <v>12.18878248974008</v>
+        <v>42.75479744136461</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.127358490566038</v>
+        <v>13.11764705882353</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1959</v>
+        <v>1514</v>
       </c>
       <c r="AE27" t="n">
-        <v>-1464</v>
+        <v>-957</v>
       </c>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
-        <v>0.5952935024825606</v>
+        <v>0.5661407329307805</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hendrita01</t>
+          <t>simmobe01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TAYLOR HENDRICKS</t>
+          <t>BEN SIMMONS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -3473,105 +3441,107 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BRK</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J28" t="n">
-        <v>856</v>
+        <v>359</v>
       </c>
       <c r="K28" t="n">
-        <v>292</v>
+        <v>92</v>
       </c>
       <c r="L28" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="M28" t="n">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="N28" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="O28" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="P28" t="n">
         <v>27</v>
       </c>
       <c r="Q28" t="n">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="R28" t="n">
-        <v>0.793</v>
+        <v>0.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.379</v>
-      </c>
+        <v>0.581</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
-        <v>0.45</v>
+        <v>0.581</v>
       </c>
       <c r="V28" t="n">
-        <v>776</v>
+        <v>416</v>
       </c>
       <c r="W28" t="n">
-        <v>19.4</v>
+        <v>27.73333333333333</v>
       </c>
       <c r="X28" t="n">
-        <v>0.9065420560747663</v>
+        <v>1.158774373259053</v>
       </c>
       <c r="Y28" t="n">
-        <v>33.73913043478261</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.0453774633062394</v>
+        <v>0.02593192868719611</v>
       </c>
       <c r="AA28" t="n">
-        <v>32.63551401869159</v>
+        <v>41.71587743732591</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.125</v>
+        <v>1.069767441860465</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Nivel 3: Above Average</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
+          <t>Nivel 4: Elite</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>3495</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>-3079</v>
+      </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
-        <v>0.5912756829622967</v>
+        <v>0.5654406074804039</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nworajo01</t>
+          <t>laravja01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JORDAN NWORA</t>
+          <t>JAKE LARAVIA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -3579,109 +3549,109 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H29" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>712</v>
+        <v>806</v>
       </c>
       <c r="K29" t="n">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="L29" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="M29" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="N29" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Q29" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="R29" t="n">
-        <v>0.83</v>
+        <v>0.826</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.442</v>
       </c>
       <c r="T29" t="n">
-        <v>0.336</v>
+        <v>0.34</v>
       </c>
       <c r="U29" t="n">
-        <v>0.462</v>
+        <v>0.389</v>
       </c>
       <c r="V29" t="n">
-        <v>182</v>
+        <v>714</v>
       </c>
       <c r="W29" t="n">
-        <v>3.5</v>
+        <v>20.4</v>
       </c>
       <c r="X29" t="n">
-        <v>0.2556179775280899</v>
+        <v>0.8858560794044665</v>
       </c>
       <c r="Y29" t="n">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.008623548922056384</v>
+        <v>0.04784240150093809</v>
       </c>
       <c r="AA29" t="n">
-        <v>9.202247191011237</v>
+        <v>31.8908188585608</v>
       </c>
       <c r="AB29" t="n">
-        <v>5.870967741935484</v>
+        <v>6.53448275862069</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 3: Above Average</t>
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>931</v>
+        <v>262</v>
       </c>
       <c r="AE29" t="n">
-        <v>-749</v>
+        <v>452</v>
       </c>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="n">
-        <v>0.5893474413349312</v>
+        <v>0.5649408835628557</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>grimequ01</t>
+          <t>walkeja02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>QUENTIN GRIMES</t>
+          <t>JARACE WALKER</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -3689,109 +3659,105 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H30" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1025</v>
+        <v>340</v>
       </c>
       <c r="K30" t="n">
-        <v>359</v>
+        <v>120</v>
       </c>
       <c r="L30" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="N30" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="O30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P30" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Q30" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="R30" t="n">
-        <v>0.756</v>
+        <v>0.889</v>
       </c>
       <c r="S30" t="n">
-        <v>0.466</v>
+        <v>0.418</v>
       </c>
       <c r="T30" t="n">
-        <v>0.338</v>
+        <v>0.4</v>
       </c>
       <c r="U30" t="n">
-        <v>0.372</v>
+        <v>0.409</v>
       </c>
       <c r="V30" t="n">
-        <v>93</v>
+        <v>345</v>
       </c>
       <c r="W30" t="n">
-        <v>1.823529411764706</v>
+        <v>10.45454545454546</v>
       </c>
       <c r="X30" t="n">
-        <v>0.09073170731707317</v>
+        <v>1.014705882352941</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.004406538734896943</v>
+        <v>0.01884730947828462</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.266341463414634</v>
+        <v>36.52941176470588</v>
       </c>
       <c r="AB30" t="n">
-        <v>5.439393939393939</v>
+        <v>3</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD30" t="n">
-        <v>1674</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>-1581</v>
-      </c>
+          <t>Nivel 4: Elite</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
-        <v>0.5875429855179959</v>
+        <v>0.5638361949222238</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>whitmca01</t>
+          <t>councri01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CAM WHITMORE</t>
+          <t>RICKY COUNCIL IV</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -3799,81 +3765,81 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H31" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>880</v>
+        <v>289</v>
       </c>
       <c r="K31" t="n">
-        <v>579</v>
+        <v>173</v>
       </c>
       <c r="L31" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="M31" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="N31" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q31" t="n">
         <v>17</v>
       </c>
-      <c r="P31" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>64</v>
-      </c>
       <c r="R31" t="n">
-        <v>0.679</v>
+        <v>0.746</v>
       </c>
       <c r="S31" t="n">
-        <v>0.538</v>
+        <v>0.525</v>
       </c>
       <c r="T31" t="n">
-        <v>0.359</v>
+        <v>0.375</v>
       </c>
       <c r="U31" t="n">
-        <v>0.454</v>
+        <v>0.482</v>
       </c>
       <c r="V31" t="n">
-        <v>983</v>
+        <v>275</v>
       </c>
       <c r="W31" t="n">
-        <v>20.91489361702128</v>
+        <v>8.59375</v>
       </c>
       <c r="X31" t="n">
-        <v>1.117045454545454</v>
+        <v>0.9515570934256056</v>
       </c>
       <c r="Y31" t="n">
-        <v>491.5</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.04889574214086749</v>
+        <v>0.01830039262660544</v>
       </c>
       <c r="AA31" t="n">
-        <v>40.21363636363636</v>
+        <v>34.2560553633218</v>
       </c>
       <c r="AB31" t="n">
-        <v>17.54545454545455</v>
+        <v>10.8125</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Nivel 4: Elite</t>
+          <t>Nivel 3: Above Average</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -3881,23 +3847,23 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
-        <v>0.5863992328651988</v>
+        <v>0.5633556051191786</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>livelde01</t>
+          <t>garlada01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DERECK LIVELY II</t>
+          <t>DARIUS GARLAND</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -3905,105 +3871,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H32" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I32" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J32" t="n">
-        <v>1294</v>
+        <v>1901</v>
       </c>
       <c r="K32" t="n">
-        <v>483</v>
+        <v>1028</v>
       </c>
       <c r="L32" t="n">
-        <v>60</v>
+        <v>373</v>
       </c>
       <c r="M32" t="n">
-        <v>378</v>
+        <v>152</v>
       </c>
       <c r="N32" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="O32" t="n">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="P32" t="n">
-        <v>50</v>
+        <v>176</v>
       </c>
       <c r="Q32" t="n">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="R32" t="n">
-        <v>0.506</v>
+        <v>0.834</v>
       </c>
       <c r="S32" t="n">
-        <v>0.752</v>
+        <v>0.501</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="U32" t="n">
-        <v>0.747</v>
+        <v>0.446</v>
       </c>
       <c r="V32" t="n">
-        <v>1441</v>
+        <v>2002</v>
       </c>
       <c r="W32" t="n">
-        <v>26.2</v>
+        <v>35.12280701754386</v>
       </c>
       <c r="X32" t="n">
-        <v>1.113601236476043</v>
+        <v>1.053129931614939</v>
       </c>
       <c r="Y32" t="n">
-        <v>34.30952380952381</v>
+        <v>35.12280701754386</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.08288754673569169</v>
+        <v>0.09845094664371773</v>
       </c>
       <c r="AA32" t="n">
-        <v>40.08964451313756</v>
+        <v>37.91267753813782</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.050000000000001</v>
+        <v>2.756032171581769</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
           <t>Nivel 4: Elite</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
+      <c r="AD32" t="n">
+        <v>2916</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>-914</v>
+      </c>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="n">
-        <v>0.5799685810547764</v>
+        <v>0.5599323081899694</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>herroty01</t>
+          <t>jackstr02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TYLER HERRO</t>
+          <t>TRAYCE JACKSON-DAVIS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -4011,104 +3981,100 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H33" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="I33" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>1407</v>
+        <v>1130</v>
       </c>
       <c r="K33" t="n">
-        <v>875</v>
+        <v>540</v>
       </c>
       <c r="L33" t="n">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="M33" t="n">
-        <v>222</v>
+        <v>341</v>
       </c>
       <c r="N33" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="P33" t="n">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="Q33" t="n">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="R33" t="n">
-        <v>0.856</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="S33" t="n">
-        <v>0.478</v>
+        <v>0.704</v>
       </c>
       <c r="T33" t="n">
-        <v>0.396</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0.441</v>
+        <v>0.702</v>
       </c>
       <c r="V33" t="n">
-        <v>1517</v>
+        <v>1444</v>
       </c>
       <c r="W33" t="n">
-        <v>36.11904761904762</v>
+        <v>21.23529411764706</v>
       </c>
       <c r="X33" t="n">
-        <v>1.07818052594172</v>
+        <v>1.27787610619469</v>
       </c>
       <c r="Y33" t="n">
-        <v>37.925</v>
+        <v>90.25</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.08956721969652241</v>
+        <v>0.06841656401023406</v>
       </c>
       <c r="AA33" t="n">
-        <v>38.81449893390192</v>
+        <v>46.00353982300884</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.654255319148936</v>
+        <v>6.585365853658536</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
           <t>Nivel 4: Elite</t>
         </is>
       </c>
-      <c r="AD33" t="n">
-        <v>2406</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>-889</v>
-      </c>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="n">
-        <v>0.5737540179292917</v>
+        <v>0.5544539381105046</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>theisda01</t>
+          <t>smithja04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DANIEL THEIS</t>
+          <t>JALEN SMITH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4121,109 +4087,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H34" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J34" t="n">
-        <v>1015</v>
+        <v>1047</v>
       </c>
       <c r="K34" t="n">
-        <v>376</v>
+        <v>601</v>
       </c>
       <c r="L34" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M34" t="n">
-        <v>244</v>
+        <v>337</v>
       </c>
       <c r="N34" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O34" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="P34" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q34" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="R34" t="n">
-        <v>0.76</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="S34" t="n">
-        <v>0.586</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="T34" t="n">
-        <v>0.366</v>
+        <v>0.424</v>
       </c>
       <c r="U34" t="n">
-        <v>0.532</v>
+        <v>0.592</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>1320</v>
       </c>
       <c r="W34" t="n">
-        <v>0.01666666666666667</v>
+        <v>21.63934426229508</v>
       </c>
       <c r="X34" t="n">
-        <v>0.0009852216748768472</v>
+        <v>1.260744985673352</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.3333333333333333</v>
+        <v>94.28571428571429</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.738213693437574e-05</v>
+        <v>0.07211144496039333</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.0354679802955665</v>
+        <v>45.38681948424068</v>
       </c>
       <c r="AB34" t="n">
-        <v>6.163934426229508</v>
+        <v>9.53968253968254</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1718</v>
+        <v>1428</v>
       </c>
       <c r="AE34" t="n">
-        <v>-1717</v>
+        <v>-108</v>
       </c>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="n">
-        <v>0.5723962866949516</v>
+        <v>0.5522797472762144</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>banede01</t>
+          <t>sensabr01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DESMOND BANE</t>
+          <t>BRICE SENSABAUGH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -4231,109 +4197,105 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H35" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I35" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="J35" t="n">
-        <v>1443</v>
+        <v>584</v>
       </c>
       <c r="K35" t="n">
-        <v>997</v>
+        <v>241</v>
       </c>
       <c r="L35" t="n">
-        <v>230</v>
+        <v>55</v>
       </c>
       <c r="M35" t="n">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="N35" t="n">
+        <v>13</v>
+      </c>
+      <c r="O35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P35" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q35" t="n">
         <v>43</v>
       </c>
-      <c r="O35" t="n">
-        <v>22</v>
-      </c>
-      <c r="P35" t="n">
-        <v>112</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>120</v>
-      </c>
       <c r="R35" t="n">
-        <v>0.87</v>
+        <v>0.902</v>
       </c>
       <c r="S35" t="n">
-        <v>0.536</v>
+        <v>0.495</v>
       </c>
       <c r="T35" t="n">
-        <v>0.381</v>
+        <v>0.296</v>
       </c>
       <c r="U35" t="n">
-        <v>0.464</v>
+        <v>0.39</v>
       </c>
       <c r="V35" t="n">
-        <v>1824</v>
+        <v>464</v>
       </c>
       <c r="W35" t="n">
-        <v>43.42857142857143</v>
+        <v>14.5</v>
       </c>
       <c r="X35" t="n">
-        <v>1.264033264033264</v>
+        <v>0.7945205479452054</v>
       </c>
       <c r="Y35" t="n">
-        <v>43.42857142857143</v>
+        <v>42.18181818181818</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.1222192441704637</v>
+        <v>0.02713291620373078</v>
       </c>
       <c r="AA35" t="n">
-        <v>45.50519750519751</v>
+        <v>28.60273972602739</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.334782608695652</v>
+        <v>4.381818181818182</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Nivel 4: Elite</t>
-        </is>
-      </c>
-      <c r="AD35" t="n">
-        <v>2591</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>-767</v>
-      </c>
+          <t>Nivel 2: Average</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="n">
-        <v>0.570638526483393</v>
+        <v>0.5518158343482438</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ballla01</t>
+          <t>strawju01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LAMELO BALL</t>
+          <t>JULIAN STRAWTHER</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -4341,109 +4303,105 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CHO</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H36" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>711</v>
+        <v>545</v>
       </c>
       <c r="K36" t="n">
-        <v>526</v>
+        <v>227</v>
       </c>
       <c r="L36" t="n">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="M36" t="n">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="N36" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P36" t="n">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="Q36" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="R36" t="n">
-        <v>0.865</v>
+        <v>0.71</v>
       </c>
       <c r="S36" t="n">
-        <v>0.5</v>
+        <v>0.488</v>
       </c>
       <c r="T36" t="n">
-        <v>0.355</v>
+        <v>0.297</v>
       </c>
       <c r="U36" t="n">
-        <v>0.433</v>
+        <v>0.369</v>
       </c>
       <c r="V36" t="n">
-        <v>1057</v>
+        <v>462</v>
       </c>
       <c r="W36" t="n">
-        <v>48.04545454545455</v>
+        <v>9.24</v>
       </c>
       <c r="X36" t="n">
-        <v>1.486638537271449</v>
+        <v>0.8477064220183487</v>
       </c>
       <c r="Y36" t="n">
-        <v>48.04545454545455</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.09143598615916955</v>
+        <v>0.02170950613223063</v>
       </c>
       <c r="AA36" t="n">
-        <v>53.51898734177215</v>
+        <v>30.51743119266055</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.988636363636364</v>
+        <v>4.829787234042553</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Nivel 4: Elite</t>
-        </is>
-      </c>
-      <c r="AD36" t="n">
-        <v>3393</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>-2336</v>
-      </c>
+          <t>Nivel 3: Above Average</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="n">
-        <v>0.5701443730017937</v>
+        <v>0.549995336928022</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mobleev01</t>
+          <t>bufkiko01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EVAN MOBLEY</t>
+          <t>KOBE BUFKIN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -4451,104 +4409,100 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H37" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="I37" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1532</v>
+        <v>196</v>
       </c>
       <c r="K37" t="n">
-        <v>785</v>
+        <v>81</v>
       </c>
       <c r="L37" t="n">
-        <v>160</v>
+        <v>27</v>
       </c>
       <c r="M37" t="n">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N37" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="O37" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="n">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="R37" t="n">
-        <v>0.719</v>
+        <v>0.5</v>
       </c>
       <c r="S37" t="n">
-        <v>0.604</v>
+        <v>0.481</v>
       </c>
       <c r="T37" t="n">
-        <v>0.373</v>
+        <v>0.225</v>
       </c>
       <c r="U37" t="n">
-        <v>0.58</v>
+        <v>0.37</v>
       </c>
       <c r="V37" t="n">
-        <v>1938</v>
+        <v>199</v>
       </c>
       <c r="W37" t="n">
-        <v>38.76</v>
+        <v>11.70588235294118</v>
       </c>
       <c r="X37" t="n">
-        <v>1.265013054830287</v>
+        <v>1.01530612244898</v>
       </c>
       <c r="Y37" t="n">
-        <v>38.76</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.09530366363412834</v>
+        <v>0.009738670842713125</v>
       </c>
       <c r="AA37" t="n">
-        <v>45.54046997389034</v>
+        <v>36.55102040816327</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.90625</v>
+        <v>3</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
           <t>Nivel 4: Elite</t>
         </is>
       </c>
-      <c r="AD37" t="n">
-        <v>2944</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>-1006</v>
-      </c>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="n">
-        <v>0.5688840018566816</v>
+        <v>0.5477808578095398</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>wallaca01</t>
+          <t>kennalu01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CASON WALLACE</t>
+          <t>LUKE KENNARD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4561,100 +4515,104 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
+        <v>27</v>
+      </c>
+      <c r="H38" t="n">
+        <v>39</v>
+      </c>
+      <c r="I38" t="n">
+        <v>22</v>
+      </c>
+      <c r="J38" t="n">
+        <v>999</v>
+      </c>
+      <c r="K38" t="n">
+        <v>429</v>
+      </c>
+      <c r="L38" t="n">
+        <v>136</v>
+      </c>
+      <c r="M38" t="n">
+        <v>113</v>
+      </c>
+      <c r="N38" t="n">
         <v>20</v>
       </c>
-      <c r="H38" t="n">
-        <v>82</v>
-      </c>
-      <c r="I38" t="n">
-        <v>13</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1692</v>
-      </c>
-      <c r="K38" t="n">
-        <v>561</v>
-      </c>
-      <c r="L38" t="n">
-        <v>120</v>
-      </c>
-      <c r="M38" t="n">
-        <v>187</v>
-      </c>
-      <c r="N38" t="n">
-        <v>76</v>
-      </c>
       <c r="O38" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="Q38" t="n">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="R38" t="n">
-        <v>0.784</v>
+        <v>0.889</v>
       </c>
       <c r="S38" t="n">
-        <v>0.572</v>
+        <v>0.442</v>
       </c>
       <c r="T38" t="n">
-        <v>0.419</v>
+        <v>0.45</v>
       </c>
       <c r="U38" t="n">
-        <v>0.491</v>
+        <v>0.448</v>
       </c>
       <c r="V38" t="n">
-        <v>1470</v>
+        <v>887</v>
       </c>
       <c r="W38" t="n">
-        <v>17.92682926829268</v>
+        <v>22.74358974358974</v>
       </c>
       <c r="X38" t="n">
-        <v>0.8687943262411347</v>
+        <v>0.8878878878878879</v>
       </c>
       <c r="Y38" t="n">
-        <v>113.0769230769231</v>
+        <v>40.31818181818182</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.06936252536214788</v>
+        <v>0.05943446797105334</v>
       </c>
       <c r="AA38" t="n">
-        <v>31.27659574468085</v>
+        <v>31.96396396396396</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.675</v>
+        <v>3.154411764705882</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
           <t>Nivel 3: Above Average</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
+      <c r="AD38" t="n">
+        <v>1586</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>-699</v>
+      </c>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="n">
-        <v>0.5633397960204723</v>
+        <v>0.5465017240459263</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>flynnma01</t>
+          <t>smartma01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MALACHI FLYNN</t>
+          <t>MARCUS SMART</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4667,109 +4625,109 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H39" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>876</v>
+        <v>605</v>
       </c>
       <c r="K39" t="n">
-        <v>380</v>
+        <v>289</v>
       </c>
       <c r="L39" t="n">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="M39" t="n">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="N39" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q39" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="R39" t="n">
-        <v>0.732</v>
+        <v>0.768</v>
       </c>
       <c r="S39" t="n">
-        <v>0.513</v>
+        <v>0.583</v>
       </c>
       <c r="T39" t="n">
-        <v>0.331</v>
+        <v>0.313</v>
       </c>
       <c r="U39" t="n">
-        <v>0.418</v>
+        <v>0.43</v>
       </c>
       <c r="V39" t="n">
-        <v>49</v>
+        <v>620</v>
       </c>
       <c r="W39" t="n">
-        <v>0.7101449275362319</v>
+        <v>31</v>
       </c>
       <c r="X39" t="n">
-        <v>0.05593607305936073</v>
+        <v>1.024793388429752</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.002321724709784411</v>
+        <v>0.04154382203162691</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.013698630136986</v>
+        <v>36.89256198347107</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.923076923076923</v>
+        <v>3.36046511627907</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>854</v>
+        <v>2281</v>
       </c>
       <c r="AE39" t="n">
-        <v>-805</v>
+        <v>-1661</v>
       </c>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="n">
-        <v>0.5631706540686908</v>
+        <v>0.5462221371711349</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cartewe01</t>
+          <t>portejo01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WENDELL CARTER JR.</t>
+          <t>JONTAY PORTER</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4777,7 +4735,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -4787,99 +4745,99 @@
         <v>24</v>
       </c>
       <c r="H40" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="I40" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
-        <v>1406</v>
+        <v>360</v>
       </c>
       <c r="K40" t="n">
-        <v>603</v>
+        <v>115</v>
       </c>
       <c r="L40" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="M40" t="n">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="N40" t="n">
+        <v>20</v>
+      </c>
+      <c r="O40" t="n">
+        <v>20</v>
+      </c>
+      <c r="P40" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q40" t="n">
         <v>35</v>
       </c>
-      <c r="O40" t="n">
-        <v>28</v>
-      </c>
-      <c r="P40" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>121</v>
-      </c>
       <c r="R40" t="n">
-        <v>0.694</v>
+        <v>0.833</v>
       </c>
       <c r="S40" t="n">
-        <v>0.626</v>
+        <v>0.455</v>
       </c>
       <c r="T40" t="n">
-        <v>0.374</v>
+        <v>0.333</v>
       </c>
       <c r="U40" t="n">
-        <v>0.525</v>
+        <v>0.385</v>
       </c>
       <c r="V40" t="n">
-        <v>1377</v>
+        <v>448</v>
       </c>
       <c r="W40" t="n">
-        <v>25.03636363636364</v>
+        <v>17.23076923076923</v>
       </c>
       <c r="X40" t="n">
-        <v>0.9793741109530584</v>
+        <v>1.244444444444444</v>
       </c>
       <c r="Y40" t="n">
-        <v>28.6875</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.07048886613770156</v>
+        <v>0.04618556701030928</v>
       </c>
       <c r="AA40" t="n">
-        <v>35.2574679943101</v>
+        <v>44.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>6.347368421052631</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Nivel 3: Above Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>2117</v>
+        <v>44</v>
       </c>
       <c r="AE40" t="n">
-        <v>-740</v>
+        <v>404</v>
       </c>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="n">
-        <v>0.5609785859000364</v>
+        <v>0.5448230702779675</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>thompam01</t>
+          <t>hylanbo01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AMEN THOMPSON</t>
+          <t>BONES HYLAND</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -4887,100 +4845,104 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H41" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
-        <v>1388</v>
+        <v>540</v>
       </c>
       <c r="K41" t="n">
-        <v>592</v>
+        <v>256</v>
       </c>
       <c r="L41" t="n">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="M41" t="n">
-        <v>409</v>
+        <v>55</v>
       </c>
       <c r="N41" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="O41" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="Q41" t="n">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="R41" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.783</v>
       </c>
       <c r="S41" t="n">
-        <v>0.595</v>
+        <v>0.457</v>
       </c>
       <c r="T41" t="n">
-        <v>0.138</v>
+        <v>0.326</v>
       </c>
       <c r="U41" t="n">
-        <v>0.536</v>
+        <v>0.386</v>
       </c>
       <c r="V41" t="n">
-        <v>1644</v>
+        <v>558</v>
       </c>
       <c r="W41" t="n">
-        <v>26.51612903225806</v>
+        <v>15.08108108108108</v>
       </c>
       <c r="X41" t="n">
-        <v>1.184438040345821</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="Y41" t="n">
-        <v>71.47826086956522</v>
+        <v>111.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.08177477118981297</v>
+        <v>0.02898400166216497</v>
       </c>
       <c r="AA41" t="n">
-        <v>42.63976945244956</v>
+        <v>37.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>3.631901840490797</v>
+        <v>2.752688172043011</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
           <t>Nivel 4: Elite</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
+      <c r="AD41" t="n">
+        <v>1438</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>-880</v>
+      </c>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="n">
-        <v>0.559028236404077</v>
+        <v>0.5441968467048691</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>burksal01</t>
+          <t>sharpsh01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ALEC BURKS</t>
+          <t>SHAEDON SHARPE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4993,32 +4955,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
+        <v>20</v>
+      </c>
+      <c r="H42" t="n">
         <v>32</v>
       </c>
-      <c r="H42" t="n">
-        <v>66</v>
-      </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>1212</v>
+        <v>1059</v>
       </c>
       <c r="K42" t="n">
-        <v>689</v>
+        <v>510</v>
       </c>
       <c r="L42" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M42" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="N42" t="n">
         <v>28</v>
@@ -5027,70 +4989,70 @@
         <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="Q42" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="R42" t="n">
-        <v>0.868</v>
+        <v>0.824</v>
       </c>
       <c r="S42" t="n">
-        <v>0.36</v>
+        <v>0.457</v>
       </c>
       <c r="T42" t="n">
-        <v>0.376</v>
+        <v>0.333</v>
       </c>
       <c r="U42" t="n">
-        <v>0.369</v>
+        <v>0.406</v>
       </c>
       <c r="V42" t="n">
-        <v>215</v>
+        <v>891</v>
       </c>
       <c r="W42" t="n">
-        <v>3.257575757575758</v>
+        <v>27.84375</v>
       </c>
       <c r="X42" t="n">
-        <v>0.1773927392739274</v>
+        <v>0.8413597733711048</v>
       </c>
       <c r="Y42" t="n">
-        <v>215</v>
+        <v>35.64</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.01018715944089078</v>
+        <v>0.05313692748091603</v>
       </c>
       <c r="AA42" t="n">
-        <v>6.386138613861386</v>
+        <v>30.28895184135977</v>
       </c>
       <c r="AB42" t="n">
-        <v>7.829545454545454</v>
+        <v>5.425531914893617</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 3: Above Average</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>2108</v>
+        <v>1410</v>
       </c>
       <c r="AE42" t="n">
-        <v>-1893</v>
+        <v>-519</v>
       </c>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="n">
-        <v>0.5580688577529321</v>
+        <v>0.5438712320157384</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>okongon01</t>
+          <t>jacksis01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ONYEKA OKONGWU</t>
+          <t>ISAIAH JACKSON</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5103,77 +5065,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H43" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I43" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
-        <v>1405</v>
+        <v>771</v>
       </c>
       <c r="K43" t="n">
-        <v>561</v>
+        <v>383</v>
       </c>
       <c r="L43" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="M43" t="n">
-        <v>376</v>
+        <v>238</v>
       </c>
       <c r="N43" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="O43" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P43" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q43" t="n">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="R43" t="n">
-        <v>0.793</v>
+        <v>0.716</v>
       </c>
       <c r="S43" t="n">
-        <v>0.676</v>
+        <v>0.677</v>
       </c>
       <c r="T43" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0.611</v>
+        <v>0.665</v>
       </c>
       <c r="V43" t="n">
-        <v>1442</v>
+        <v>1075</v>
       </c>
       <c r="W43" t="n">
-        <v>26.21818181818182</v>
+        <v>18.22033898305085</v>
       </c>
       <c r="X43" t="n">
-        <v>1.026334519572954</v>
+        <v>1.394293125810635</v>
       </c>
       <c r="Y43" t="n">
-        <v>180.25</v>
+        <v>358.3333333333333</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.07056866007634335</v>
+        <v>0.05872712373668396</v>
       </c>
       <c r="AA43" t="n">
-        <v>36.94804270462633</v>
+        <v>50.19455252918288</v>
       </c>
       <c r="AB43" t="n">
-        <v>7.581081081081081</v>
+        <v>7.66</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -5181,26 +5143,26 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>2122</v>
+        <v>1234</v>
       </c>
       <c r="AE43" t="n">
-        <v>-680</v>
+        <v>-159</v>
       </c>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="n">
-        <v>0.5523781028009168</v>
+        <v>0.5436522664733316</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>simonan01</t>
+          <t>wallaca01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ANFERNEE SIMONS</t>
+          <t>CASON WALLACE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5213,109 +5175,105 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="I44" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="J44" t="n">
-        <v>1582</v>
+        <v>1692</v>
       </c>
       <c r="K44" t="n">
-        <v>1039</v>
+        <v>561</v>
       </c>
       <c r="L44" t="n">
-        <v>255</v>
+        <v>120</v>
       </c>
       <c r="M44" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="N44" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="O44" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="P44" t="n">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="Q44" t="n">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="R44" t="n">
-        <v>0.916</v>
+        <v>0.784</v>
       </c>
       <c r="S44" t="n">
-        <v>0.472</v>
+        <v>0.572</v>
       </c>
       <c r="T44" t="n">
-        <v>0.385</v>
+        <v>0.419</v>
       </c>
       <c r="U44" t="n">
-        <v>0.43</v>
+        <v>0.491</v>
       </c>
       <c r="V44" t="n">
-        <v>1693</v>
+        <v>1470</v>
       </c>
       <c r="W44" t="n">
-        <v>36.80434782608695</v>
+        <v>17.92682926829268</v>
       </c>
       <c r="X44" t="n">
-        <v>1.070164348925411</v>
+        <v>0.8687943262411347</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.80434782608695</v>
+        <v>113.0769230769231</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.1009661259541985</v>
+        <v>0.06936252536214788</v>
       </c>
       <c r="AA44" t="n">
-        <v>38.52591656131479</v>
+        <v>31.27659574468085</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.074509803921568</v>
+        <v>4.675</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Nivel 4: Elite</t>
-        </is>
-      </c>
-      <c r="AD44" t="n">
-        <v>2161</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>-468</v>
-      </c>
+          <t>Nivel 3: Above Average</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="n">
-        <v>0.5523777543540238</v>
+        <v>0.5435637195427881</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>murphtr02</t>
+          <t>vandeja01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TREY MURPHY III</t>
+          <t>JARRED VANDERBILT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -5323,109 +5281,109 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H45" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="J45" t="n">
-        <v>1690</v>
+        <v>581</v>
       </c>
       <c r="K45" t="n">
-        <v>842</v>
+        <v>150</v>
       </c>
       <c r="L45" t="n">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="M45" t="n">
-        <v>280</v>
+        <v>138</v>
       </c>
       <c r="N45" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="O45" t="n">
+        <v>5</v>
+      </c>
+      <c r="P45" t="n">
         <v>28</v>
       </c>
-      <c r="P45" t="n">
-        <v>34</v>
-      </c>
       <c r="Q45" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="R45" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="S45" t="n">
-        <v>0.602</v>
+        <v>0.586</v>
       </c>
       <c r="T45" t="n">
-        <v>0.38</v>
+        <v>0.296</v>
       </c>
       <c r="U45" t="n">
-        <v>0.443</v>
+        <v>0.518</v>
       </c>
       <c r="V45" t="n">
-        <v>1795</v>
+        <v>479</v>
       </c>
       <c r="W45" t="n">
-        <v>31.49122807017544</v>
+        <v>16.51724137931035</v>
       </c>
       <c r="X45" t="n">
-        <v>1.062130177514793</v>
+        <v>0.8244406196213425</v>
       </c>
       <c r="Y45" t="n">
-        <v>78.04347826086956</v>
+        <v>79.83333333333333</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.0871401524345842</v>
+        <v>0.02334307992202729</v>
       </c>
       <c r="AA45" t="n">
-        <v>38.23668639053254</v>
+        <v>29.67986230636833</v>
       </c>
       <c r="AB45" t="n">
-        <v>6.790322580645161</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Nivel 4: Elite</t>
+          <t>Nivel 2: Average</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>2310</v>
+        <v>1788</v>
       </c>
       <c r="AE45" t="n">
-        <v>-515</v>
+        <v>-1309</v>
       </c>
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="n">
-        <v>0.5494308293564478</v>
+        <v>0.5413521360561594</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>moranja01</t>
+          <t>thompau01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JA MORANT</t>
+          <t>AUSAR THOMPSON</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5433,109 +5391,105 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H46" t="n">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="I46" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="J46" t="n">
-        <v>318</v>
+        <v>1583</v>
       </c>
       <c r="K46" t="n">
-        <v>226</v>
+        <v>556</v>
       </c>
       <c r="L46" t="n">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="M46" t="n">
-        <v>50</v>
+        <v>402</v>
       </c>
       <c r="N46" t="n">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="P46" t="n">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="Q46" t="n">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="R46" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.597</v>
       </c>
       <c r="S46" t="n">
-        <v>0.555</v>
+        <v>0.575</v>
       </c>
       <c r="T46" t="n">
-        <v>0.275</v>
+        <v>0.186</v>
       </c>
       <c r="U46" t="n">
-        <v>0.471</v>
+        <v>0.483</v>
       </c>
       <c r="V46" t="n">
-        <v>431</v>
+        <v>1566</v>
       </c>
       <c r="W46" t="n">
-        <v>47.88888888888889</v>
+        <v>24.85714285714286</v>
       </c>
       <c r="X46" t="n">
-        <v>1.355345911949686</v>
+        <v>0.9892608970309539</v>
       </c>
       <c r="Y46" t="n">
-        <v>47.88888888888889</v>
+        <v>41.21052631578947</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.02887965692843742</v>
+        <v>0.1130849220103986</v>
       </c>
       <c r="AA46" t="n">
-        <v>48.79245283018868</v>
+        <v>35.61339229311434</v>
       </c>
       <c r="AB46" t="n">
-        <v>3.095890410958904</v>
+        <v>4.633333333333334</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Nivel 4: Elite</t>
-        </is>
-      </c>
-      <c r="AD46" t="n">
-        <v>2856</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>-2425</v>
-      </c>
+          <t>Nivel 3: Above Average</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="n">
-        <v>0.5474987196679318</v>
+        <v>0.5410348063581423</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pippesc02</t>
+          <t>butleja02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SCOTTY PIPPEN JR.</t>
+          <t>JARED BUTLER</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -5543,7 +5497,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5553,67 +5507,67 @@
         <v>23</v>
       </c>
       <c r="H47" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>527</v>
+        <v>566</v>
       </c>
       <c r="K47" t="n">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="L47" t="n">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="M47" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="N47" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P47" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="Q47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R47" t="n">
-        <v>0.745</v>
+        <v>0.861</v>
       </c>
       <c r="S47" t="n">
-        <v>0.534</v>
+        <v>0.602</v>
       </c>
       <c r="T47" t="n">
-        <v>0.417</v>
+        <v>0.308</v>
       </c>
       <c r="U47" t="n">
-        <v>0.493</v>
+        <v>0.488</v>
       </c>
       <c r="V47" t="n">
-        <v>631</v>
+        <v>653</v>
       </c>
       <c r="W47" t="n">
-        <v>30.04761904761905</v>
+        <v>16.325</v>
       </c>
       <c r="X47" t="n">
-        <v>1.197343453510436</v>
+        <v>1.153710247349823</v>
       </c>
       <c r="Y47" t="n">
-        <v>39.4375</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.04228088984186545</v>
+        <v>0.03942046483549653</v>
       </c>
       <c r="AA47" t="n">
-        <v>43.10436432637571</v>
+        <v>41.53356890459364</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.76530612244898</v>
+        <v>1.992063492063492</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -5621,26 +5575,26 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>24</v>
+        <v>392</v>
       </c>
       <c r="AE47" t="n">
-        <v>607</v>
+        <v>261</v>
       </c>
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="n">
-        <v>0.5471279899966602</v>
+        <v>0.5404858723126773</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>browntr01</t>
+          <t>blackle01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TROY BROWN JR.</t>
+          <t>LEAKY BLACK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5653,7 +5607,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>CHO</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5663,99 +5617,95 @@
         <v>24</v>
       </c>
       <c r="H48" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="I48" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>827</v>
+        <v>284</v>
       </c>
       <c r="K48" t="n">
-        <v>247</v>
+        <v>69</v>
       </c>
       <c r="L48" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="M48" t="n">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="N48" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P48" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="R48" t="n">
-        <v>0.865</v>
+        <v>0.667</v>
       </c>
       <c r="S48" t="n">
-        <v>0.435</v>
+        <v>0.5</v>
       </c>
       <c r="T48" t="n">
-        <v>0.333</v>
+        <v>0.45</v>
       </c>
       <c r="U48" t="n">
-        <v>0.372</v>
+        <v>0.481</v>
       </c>
       <c r="V48" t="n">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="W48" t="n">
-        <v>4.305084745762712</v>
+        <v>8.961538461538462</v>
       </c>
       <c r="X48" t="n">
-        <v>0.3071342200725514</v>
+        <v>0.8204225352112676</v>
       </c>
       <c r="Y48" t="n">
-        <v>16.93333333333333</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.01203506278133144</v>
+        <v>0.02015570934256055</v>
       </c>
       <c r="AA48" t="n">
-        <v>11.05683192261185</v>
+        <v>29.53521126760564</v>
       </c>
       <c r="AB48" t="n">
-        <v>4.116666666666666</v>
+        <v>2.875</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
-        </is>
-      </c>
-      <c r="AD48" t="n">
-        <v>1677</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>-1423</v>
-      </c>
+          <t>Nivel 2: Average</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="n">
-        <v>0.5466136511020461</v>
+        <v>0.5396222334544123</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mathube01</t>
+          <t>markkla01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BENNEDICT MATHURIN</t>
+          <t>LAURI MARKKANEN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -5763,109 +5713,109 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H49" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="J49" t="n">
-        <v>1538</v>
+        <v>1820</v>
       </c>
       <c r="K49" t="n">
-        <v>856</v>
+        <v>1278</v>
       </c>
       <c r="L49" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="M49" t="n">
-        <v>234</v>
+        <v>449</v>
       </c>
       <c r="N49" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="O49" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="P49" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="Q49" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="R49" t="n">
-        <v>0.821</v>
+        <v>0.899</v>
       </c>
       <c r="S49" t="n">
-        <v>0.481</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="T49" t="n">
-        <v>0.374</v>
+        <v>0.399</v>
       </c>
       <c r="U49" t="n">
-        <v>0.446</v>
+        <v>0.48</v>
       </c>
       <c r="V49" t="n">
-        <v>1353</v>
+        <v>2297</v>
       </c>
       <c r="W49" t="n">
-        <v>22.93220338983051</v>
+        <v>41.76363636363637</v>
       </c>
       <c r="X49" t="n">
-        <v>0.8797139141742523</v>
+        <v>1.262087912087912</v>
       </c>
       <c r="Y49" t="n">
-        <v>71.21052631578948</v>
+        <v>41.76363636363637</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.07391423108440316</v>
+        <v>0.134319630430969</v>
       </c>
       <c r="AA49" t="n">
-        <v>31.66970091027308</v>
+        <v>45.43516483516483</v>
       </c>
       <c r="AB49" t="n">
-        <v>7.19327731092437</v>
+        <v>11.61818181818182</v>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Nivel 3: Above Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1799</v>
+        <v>2831</v>
       </c>
       <c r="AE49" t="n">
-        <v>-446</v>
+        <v>-534</v>
       </c>
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="n">
-        <v>0.5451132316735683</v>
+        <v>0.5392128836984191</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>clownno01</t>
+          <t>jacksan01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NOAH CLOWNEY</t>
+          <t>ANDRE JACKSON JR.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -5873,81 +5823,81 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BRK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H50" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J50" t="n">
-        <v>370</v>
+        <v>572</v>
       </c>
       <c r="K50" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="L50" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="M50" t="n">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="N50" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O50" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P50" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="Q50" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="R50" t="n">
-        <v>0.7</v>
+        <v>0.727</v>
       </c>
       <c r="S50" t="n">
-        <v>0.633</v>
+        <v>0.611</v>
       </c>
       <c r="T50" t="n">
-        <v>0.364</v>
+        <v>0.37</v>
       </c>
       <c r="U50" t="n">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="V50" t="n">
-        <v>335</v>
+        <v>396</v>
       </c>
       <c r="W50" t="n">
-        <v>14.56521739130435</v>
+        <v>6.947368421052632</v>
       </c>
       <c r="X50" t="n">
-        <v>0.9054054054054054</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="Y50" t="n">
-        <v>83.75</v>
+        <v>49.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.02088268295723725</v>
+        <v>0.02015985338288449</v>
       </c>
       <c r="AA50" t="n">
-        <v>32.5945945945946</v>
+        <v>24.92307692307692</v>
       </c>
       <c r="AB50" t="n">
-        <v>7.388888888888889</v>
+        <v>2.5</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Nivel 3: Above Average</t>
+          <t>Nivel 2: Average</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -5955,23 +5905,23 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="n">
-        <v>0.5440802086162426</v>
+        <v>0.5363264118556926</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jemistr01</t>
+          <t>jonesco02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TREY JEMISON</t>
+          <t>COLBY JONES</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -5979,79 +5929,81 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H51" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I51" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>573</v>
+        <v>192</v>
       </c>
       <c r="K51" t="n">
-        <v>171</v>
+        <v>64</v>
       </c>
       <c r="L51" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M51" t="n">
-        <v>134</v>
+        <v>40</v>
       </c>
       <c r="N51" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O51" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="P51" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Q51" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="R51" t="n">
-        <v>0.84</v>
+        <v>0.545</v>
       </c>
       <c r="S51" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="T51" t="inlineStr"/>
+        <v>0.531</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.091</v>
+      </c>
       <c r="U51" t="n">
-        <v>0.551</v>
+        <v>0.394</v>
       </c>
       <c r="V51" t="n">
-        <v>-1</v>
+        <v>172</v>
       </c>
       <c r="W51" t="n">
-        <v>-0.04</v>
+        <v>5.733333333333333</v>
       </c>
       <c r="X51" t="n">
-        <v>-0.001745200698080279</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="Y51" t="n">
-        <v>-0.07142857142857142</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>-4.738213693437574e-05</v>
+        <v>0.008238731618527567</v>
       </c>
       <c r="AA51" t="n">
-        <v>-0.06282722513089005</v>
+        <v>32.25</v>
       </c>
       <c r="AB51" t="n">
-        <v>6.333333333333333</v>
+        <v>3.2</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Nivel 1: Below Average</t>
+          <t>Nivel 3: Above Average</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr"/>
@@ -6059,7 +6011,7 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="n">
-        <v>0.5423280115319352</v>
+        <v>0.5358854523747906</v>
       </c>
     </row>
   </sheetData>

--- a/src - analytics/top_50_previsoes.xlsx
+++ b/src - analytics/top_50_previsoes.xlsx
@@ -707,7 +707,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>0.650338236848668</v>
+        <v>0.6513504976142183</v>
       </c>
     </row>
     <row r="3">
@@ -817,7 +817,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>0.6467077820108499</v>
+        <v>0.6471949453105131</v>
       </c>
     </row>
     <row r="4">
@@ -1029,7 +1029,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>0.631316291579607</v>
+        <v>0.631341778141238</v>
       </c>
     </row>
     <row r="6">
@@ -1245,7 +1245,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>0.6277049815372435</v>
+        <v>0.6276606671559726</v>
       </c>
     </row>
     <row r="8">
@@ -1355,7 +1355,7 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>0.6171617140402206</v>
+        <v>0.6166872006018518</v>
       </c>
     </row>
     <row r="9">
@@ -1571,7 +1571,7 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>0.6094643480276508</v>
+        <v>0.6099515113273141</v>
       </c>
     </row>
     <row r="11">
@@ -1681,7 +1681,7 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>0.6038305573573519</v>
+        <v>0.6033175731087355</v>
       </c>
     </row>
     <row r="12">
@@ -1791,7 +1791,7 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>0.5935210119967944</v>
+        <v>0.5934766976155235</v>
       </c>
     </row>
     <row r="13">
@@ -2113,7 +2113,7 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="n">
-        <v>0.5850650024355742</v>
+        <v>0.5849721452927171</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>0.5843281535153161</v>
+        <v>0.5846364541647084</v>
       </c>
     </row>
     <row r="17">
@@ -2439,7 +2439,7 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>0.5767584356561199</v>
+        <v>0.5767641174743018</v>
       </c>
     </row>
     <row r="19">
@@ -2659,7 +2659,7 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="n">
-        <v>0.5740312665957932</v>
+        <v>0.5739869522145223</v>
       </c>
     </row>
     <row r="21">
@@ -2775,17 +2775,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>prospol01</t>
+          <t>willima07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OLIVIER-MAXENCE PROSPER</t>
+          <t>MARK WILLIAMS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2793,105 +2793,107 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHO</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H22" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>336</v>
+        <v>508</v>
       </c>
       <c r="K22" t="n">
-        <v>121</v>
+        <v>242</v>
       </c>
       <c r="L22" t="n">
         <v>22</v>
       </c>
       <c r="M22" t="n">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.719</v>
       </c>
       <c r="S22" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.289</v>
-      </c>
+        <v>0.649</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
-        <v>0.385</v>
+        <v>0.649</v>
       </c>
       <c r="V22" t="n">
-        <v>267</v>
+        <v>607</v>
       </c>
       <c r="W22" t="n">
-        <v>6.675</v>
+        <v>31.94736842105263</v>
       </c>
       <c r="X22" t="n">
-        <v>0.7946428571428571</v>
+        <v>1.19488188976378</v>
       </c>
       <c r="Y22" t="n">
-        <v>267</v>
+        <v>31.94736842105263</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.01535806729939603</v>
+        <v>0.05250865051903114</v>
       </c>
       <c r="AA22" t="n">
-        <v>28.60714285714285</v>
+        <v>43.01574803149607</v>
       </c>
       <c r="AB22" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Nivel 2: Average</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
+          <t>Nivel 4: Elite</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>978</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-371</v>
+      </c>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="n">
-        <v>0.5721092020284226</v>
+        <v>0.5717725538363014</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>willima07</t>
+          <t>prospol01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MARK WILLIAMS</t>
+          <t>OLIVIER-MAXENCE PROSPER</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2899,91 +2901,89 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CHO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H23" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>508</v>
+        <v>336</v>
       </c>
       <c r="K23" t="n">
-        <v>242</v>
+        <v>121</v>
       </c>
       <c r="L23" t="n">
         <v>22</v>
       </c>
       <c r="M23" t="n">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="N23" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q23" t="n">
         <v>20</v>
       </c>
-      <c r="P23" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>50</v>
-      </c>
       <c r="R23" t="n">
-        <v>0.719</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="T23" t="inlineStr"/>
+        <v>0.458</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.289</v>
+      </c>
       <c r="U23" t="n">
-        <v>0.649</v>
+        <v>0.385</v>
       </c>
       <c r="V23" t="n">
-        <v>607</v>
+        <v>267</v>
       </c>
       <c r="W23" t="n">
-        <v>31.94736842105263</v>
+        <v>6.675</v>
       </c>
       <c r="X23" t="n">
-        <v>1.19488188976378</v>
+        <v>0.7946428571428571</v>
       </c>
       <c r="Y23" t="n">
-        <v>31.94736842105263</v>
+        <v>267</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.05250865051903114</v>
+        <v>0.01535806729939603</v>
       </c>
       <c r="AA23" t="n">
-        <v>43.01574803149607</v>
+        <v>28.60714285714285</v>
       </c>
       <c r="AB23" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Nivel 4: Elite</t>
-        </is>
-      </c>
-      <c r="AD23" t="n">
-        <v>978</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>-371</v>
-      </c>
+          <t>Nivel 2: Average</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="n">
-        <v>0.5717725538363014</v>
+        <v>0.5714323727601299</v>
       </c>
     </row>
     <row r="24">
@@ -3091,7 +3091,7 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="n">
-        <v>0.5695564455146348</v>
+        <v>0.5693445788264314</v>
       </c>
     </row>
     <row r="25">
@@ -3307,7 +3307,7 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="n">
-        <v>0.5665517955243703</v>
+        <v>0.5664620258766737</v>
       </c>
     </row>
     <row r="27">
@@ -3417,7 +3417,7 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
-        <v>0.5661407329307805</v>
+        <v>0.5661662194924116</v>
       </c>
     </row>
     <row r="28">
@@ -3525,7 +3525,7 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
-        <v>0.5654406074804039</v>
+        <v>0.5657489081297963</v>
       </c>
     </row>
     <row r="29">
@@ -3635,7 +3635,7 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="n">
-        <v>0.5649408835628557</v>
+        <v>0.5649465653810375</v>
       </c>
     </row>
     <row r="30">
@@ -3741,7 +3741,7 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
-        <v>0.5638361949222238</v>
+        <v>0.563861681483855</v>
       </c>
     </row>
     <row r="31">
@@ -3847,7 +3847,7 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
-        <v>0.5633556051191786</v>
+        <v>0.5633810916808097</v>
       </c>
     </row>
     <row r="32">
@@ -3957,7 +3957,7 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="n">
-        <v>0.5599323081899694</v>
+        <v>0.5602010822592891</v>
       </c>
     </row>
     <row r="33">
@@ -4173,7 +4173,7 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="n">
-        <v>0.5522797472762144</v>
+        <v>0.5522354328949435</v>
       </c>
     </row>
     <row r="35">
@@ -4385,7 +4385,7 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="n">
-        <v>0.549995336928022</v>
+        <v>0.550171262853948</v>
       </c>
     </row>
     <row r="37">
@@ -4497,17 +4497,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kennalu01</t>
+          <t>smartma01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LUKE KENNARD</t>
+          <t>MARCUS SMART</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -4522,102 +4522,102 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H38" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>999</v>
+        <v>605</v>
       </c>
       <c r="K38" t="n">
-        <v>429</v>
+        <v>289</v>
       </c>
       <c r="L38" t="n">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="M38" t="n">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="N38" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P38" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="Q38" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="R38" t="n">
-        <v>0.889</v>
+        <v>0.768</v>
       </c>
       <c r="S38" t="n">
-        <v>0.442</v>
+        <v>0.583</v>
       </c>
       <c r="T38" t="n">
-        <v>0.45</v>
+        <v>0.313</v>
       </c>
       <c r="U38" t="n">
-        <v>0.448</v>
+        <v>0.43</v>
       </c>
       <c r="V38" t="n">
-        <v>887</v>
+        <v>620</v>
       </c>
       <c r="W38" t="n">
-        <v>22.74358974358974</v>
+        <v>31</v>
       </c>
       <c r="X38" t="n">
-        <v>0.8878878878878879</v>
+        <v>1.024793388429752</v>
       </c>
       <c r="Y38" t="n">
-        <v>40.31818181818182</v>
+        <v>31</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.05943446797105334</v>
+        <v>0.04154382203162691</v>
       </c>
       <c r="AA38" t="n">
-        <v>31.96396396396396</v>
+        <v>36.89256198347107</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.154411764705882</v>
+        <v>3.36046511627907</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Nivel 3: Above Average</t>
+          <t>Nivel 4: Elite</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1586</v>
+        <v>2281</v>
       </c>
       <c r="AE38" t="n">
-        <v>-699</v>
+        <v>-1661</v>
       </c>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="n">
-        <v>0.5465017240459263</v>
+        <v>0.5465759989597527</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>smartma01</t>
+          <t>kennalu01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MARCUS SMART</t>
+          <t>LUKE KENNARD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -4632,86 +4632,86 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H39" t="n">
+        <v>39</v>
+      </c>
+      <c r="I39" t="n">
+        <v>22</v>
+      </c>
+      <c r="J39" t="n">
+        <v>999</v>
+      </c>
+      <c r="K39" t="n">
+        <v>429</v>
+      </c>
+      <c r="L39" t="n">
+        <v>136</v>
+      </c>
+      <c r="M39" t="n">
+        <v>113</v>
+      </c>
+      <c r="N39" t="n">
         <v>20</v>
       </c>
-      <c r="I39" t="n">
-        <v>20</v>
-      </c>
-      <c r="J39" t="n">
-        <v>605</v>
-      </c>
-      <c r="K39" t="n">
-        <v>289</v>
-      </c>
-      <c r="L39" t="n">
-        <v>86</v>
-      </c>
-      <c r="M39" t="n">
-        <v>53</v>
-      </c>
-      <c r="N39" t="n">
-        <v>41</v>
-      </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="Q39" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="R39" t="n">
-        <v>0.768</v>
+        <v>0.889</v>
       </c>
       <c r="S39" t="n">
-        <v>0.583</v>
+        <v>0.442</v>
       </c>
       <c r="T39" t="n">
-        <v>0.313</v>
+        <v>0.45</v>
       </c>
       <c r="U39" t="n">
-        <v>0.43</v>
+        <v>0.448</v>
       </c>
       <c r="V39" t="n">
-        <v>620</v>
+        <v>887</v>
       </c>
       <c r="W39" t="n">
-        <v>31</v>
+        <v>22.74358974358974</v>
       </c>
       <c r="X39" t="n">
-        <v>1.024793388429752</v>
+        <v>0.8878878878878879</v>
       </c>
       <c r="Y39" t="n">
-        <v>31</v>
+        <v>40.31818181818182</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.04154382203162691</v>
+        <v>0.05943446797105334</v>
       </c>
       <c r="AA39" t="n">
-        <v>36.89256198347107</v>
+        <v>31.96396396396396</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.36046511627907</v>
+        <v>3.154411764705882</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Nivel 4: Elite</t>
+          <t>Nivel 3: Above Average</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>2281</v>
+        <v>1586</v>
       </c>
       <c r="AE39" t="n">
-        <v>-1661</v>
+        <v>-699</v>
       </c>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="n">
-        <v>0.5462221371711349</v>
+        <v>0.5464088669030691</v>
       </c>
     </row>
     <row r="40">
@@ -4821,7 +4821,7 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="n">
-        <v>0.5448230702779675</v>
+        <v>0.5448287520961493</v>
       </c>
     </row>
     <row r="41">
@@ -4931,18 +4931,18 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="n">
-        <v>0.5441968467048691</v>
+        <v>0.544202528523051</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sharpsh01</t>
+          <t>wallaca01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SHAEDON SHARPE</t>
+          <t>CASON WALLACE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -4965,99 +4965,95 @@
         <v>20</v>
       </c>
       <c r="H42" t="n">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J42" t="n">
-        <v>1059</v>
+        <v>1692</v>
       </c>
       <c r="K42" t="n">
-        <v>510</v>
+        <v>561</v>
       </c>
       <c r="L42" t="n">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="M42" t="n">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="N42" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="O42" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="P42" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="Q42" t="n">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="R42" t="n">
-        <v>0.824</v>
+        <v>0.784</v>
       </c>
       <c r="S42" t="n">
-        <v>0.457</v>
+        <v>0.572</v>
       </c>
       <c r="T42" t="n">
-        <v>0.333</v>
+        <v>0.419</v>
       </c>
       <c r="U42" t="n">
-        <v>0.406</v>
+        <v>0.491</v>
       </c>
       <c r="V42" t="n">
-        <v>891</v>
+        <v>1470</v>
       </c>
       <c r="W42" t="n">
-        <v>27.84375</v>
+        <v>17.92682926829268</v>
       </c>
       <c r="X42" t="n">
-        <v>0.8413597733711048</v>
+        <v>0.8687943262411347</v>
       </c>
       <c r="Y42" t="n">
-        <v>35.64</v>
+        <v>113.0769230769231</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.05313692748091603</v>
+        <v>0.06936252536214788</v>
       </c>
       <c r="AA42" t="n">
-        <v>30.28895184135977</v>
+        <v>31.27659574468085</v>
       </c>
       <c r="AB42" t="n">
-        <v>5.425531914893617</v>
+        <v>4.675</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
           <t>Nivel 3: Above Average</t>
         </is>
       </c>
-      <c r="AD42" t="n">
-        <v>1410</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>-519</v>
-      </c>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="n">
-        <v>0.5438712320157384</v>
+        <v>0.5440194051615173</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>jacksis01</t>
+          <t>sharpsh01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ISAIAH JACKSON</t>
+          <t>SHAEDON SHARPE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -5065,109 +5061,109 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>771</v>
+        <v>1059</v>
       </c>
       <c r="K43" t="n">
-        <v>383</v>
+        <v>510</v>
       </c>
       <c r="L43" t="n">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="M43" t="n">
-        <v>238</v>
+        <v>160</v>
       </c>
       <c r="N43" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O43" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="P43" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="Q43" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="R43" t="n">
-        <v>0.716</v>
+        <v>0.824</v>
       </c>
       <c r="S43" t="n">
-        <v>0.677</v>
+        <v>0.457</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="U43" t="n">
-        <v>0.665</v>
+        <v>0.406</v>
       </c>
       <c r="V43" t="n">
-        <v>1075</v>
+        <v>891</v>
       </c>
       <c r="W43" t="n">
-        <v>18.22033898305085</v>
+        <v>27.84375</v>
       </c>
       <c r="X43" t="n">
-        <v>1.394293125810635</v>
+        <v>0.8413597733711048</v>
       </c>
       <c r="Y43" t="n">
-        <v>358.3333333333333</v>
+        <v>35.64</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.05872712373668396</v>
+        <v>0.05313692748091603</v>
       </c>
       <c r="AA43" t="n">
-        <v>50.19455252918288</v>
+        <v>30.28895184135977</v>
       </c>
       <c r="AB43" t="n">
-        <v>7.66</v>
+        <v>5.425531914893617</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Nivel 4: Elite</t>
+          <t>Nivel 3: Above Average</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1234</v>
+        <v>1410</v>
       </c>
       <c r="AE43" t="n">
-        <v>-159</v>
+        <v>-519</v>
       </c>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="n">
-        <v>0.5436522664733316</v>
+        <v>0.5438712320157384</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>wallaca01</t>
+          <t>jacksis01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CASON WALLACE</t>
+          <t>ISAIAH JACKSON</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -5175,89 +5171,93 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H44" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="I44" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>1692</v>
+        <v>771</v>
       </c>
       <c r="K44" t="n">
-        <v>561</v>
+        <v>383</v>
       </c>
       <c r="L44" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="M44" t="n">
-        <v>187</v>
+        <v>238</v>
       </c>
       <c r="N44" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="O44" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="P44" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q44" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="R44" t="n">
-        <v>0.784</v>
+        <v>0.716</v>
       </c>
       <c r="S44" t="n">
-        <v>0.572</v>
+        <v>0.677</v>
       </c>
       <c r="T44" t="n">
-        <v>0.419</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0.491</v>
+        <v>0.665</v>
       </c>
       <c r="V44" t="n">
-        <v>1470</v>
+        <v>1075</v>
       </c>
       <c r="W44" t="n">
-        <v>17.92682926829268</v>
+        <v>18.22033898305085</v>
       </c>
       <c r="X44" t="n">
-        <v>0.8687943262411347</v>
+        <v>1.394293125810635</v>
       </c>
       <c r="Y44" t="n">
-        <v>113.0769230769231</v>
+        <v>358.3333333333333</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.06936252536214788</v>
+        <v>0.05872712373668396</v>
       </c>
       <c r="AA44" t="n">
-        <v>31.27659574468085</v>
+        <v>50.19455252918288</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.675</v>
+        <v>7.66</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Nivel 3: Above Average</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
+          <t>Nivel 4: Elite</t>
+        </is>
+      </c>
+      <c r="AD44" t="n">
+        <v>1234</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>-159</v>
+      </c>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="n">
-        <v>0.5435637195427881</v>
+        <v>0.5436522664733316</v>
       </c>
     </row>
     <row r="45">
@@ -5689,7 +5689,7 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="n">
-        <v>0.5396222334544123</v>
+        <v>0.5396477200160434</v>
       </c>
     </row>
     <row r="49">
@@ -5799,18 +5799,18 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="n">
-        <v>0.5392128836984191</v>
+        <v>0.5393069745530279</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>jacksan01</t>
+          <t>jonesco02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ANDRE JACKSON JR.</t>
+          <t>COLBY JONES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5823,81 +5823,81 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H50" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="I50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>572</v>
+        <v>192</v>
       </c>
       <c r="K50" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="L50" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M50" t="n">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="N50" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="O50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P50" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="Q50" t="n">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="R50" t="n">
-        <v>0.727</v>
+        <v>0.545</v>
       </c>
       <c r="S50" t="n">
-        <v>0.611</v>
+        <v>0.531</v>
       </c>
       <c r="T50" t="n">
-        <v>0.37</v>
+        <v>0.091</v>
       </c>
       <c r="U50" t="n">
-        <v>0.5</v>
+        <v>0.394</v>
       </c>
       <c r="V50" t="n">
-        <v>396</v>
+        <v>172</v>
       </c>
       <c r="W50" t="n">
-        <v>6.947368421052632</v>
+        <v>5.733333333333333</v>
       </c>
       <c r="X50" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="Y50" t="n">
-        <v>49.5</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.02015985338288449</v>
+        <v>0.008238731618527567</v>
       </c>
       <c r="AA50" t="n">
-        <v>24.92307692307692</v>
+        <v>32.25</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Nivel 2: Average</t>
+          <t>Nivel 3: Above Average</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -5905,18 +5905,18 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="n">
-        <v>0.5363264118556926</v>
+        <v>0.5363726156744538</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jonesco02</t>
+          <t>jacksan01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COLBY JONES</t>
+          <t>ANDRE JACKSON JR.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5929,81 +5929,81 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H51" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J51" t="n">
-        <v>192</v>
+        <v>572</v>
       </c>
       <c r="K51" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="L51" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="M51" t="n">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P51" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="Q51" t="n">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="R51" t="n">
-        <v>0.545</v>
+        <v>0.727</v>
       </c>
       <c r="S51" t="n">
-        <v>0.531</v>
+        <v>0.611</v>
       </c>
       <c r="T51" t="n">
-        <v>0.091</v>
+        <v>0.37</v>
       </c>
       <c r="U51" t="n">
-        <v>0.394</v>
+        <v>0.5</v>
       </c>
       <c r="V51" t="n">
-        <v>172</v>
+        <v>396</v>
       </c>
       <c r="W51" t="n">
-        <v>5.733333333333333</v>
+        <v>6.947368421052632</v>
       </c>
       <c r="X51" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.008238731618527567</v>
+        <v>0.02015985338288449</v>
       </c>
       <c r="AA51" t="n">
-        <v>32.25</v>
+        <v>24.92307692307692</v>
       </c>
       <c r="AB51" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Nivel 3: Above Average</t>
+          <t>Nivel 2: Average</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr"/>
@@ -6011,7 +6011,7 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="n">
-        <v>0.5358854523747906</v>
+        <v>0.5363264118556926</v>
       </c>
     </row>
   </sheetData>
